--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistemas\Pré-Atendimento\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C0F7C3E-D647-4A39-9174-C913EFE5C6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58471B39-7358-43E0-B62D-666381B0F20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="100">
   <si>
     <t>nome</t>
   </si>
@@ -111,9 +111,6 @@
     <t>Pedra Rachão</t>
   </si>
   <si>
-    <t>int</t>
-  </si>
-  <si>
     <t>un</t>
   </si>
   <si>
@@ -129,23 +126,222 @@
     <t>Azulejo</t>
   </si>
   <si>
-    <t>Tinta Látex</t>
-  </si>
-  <si>
-    <t>L</t>
-  </si>
-  <si>
-    <t>Tinta Acrílica</t>
-  </si>
-  <si>
-    <t>Tinta Esmalte</t>
+    <t>Brita 0</t>
+  </si>
+  <si>
+    <t>Pó de Pedra</t>
+  </si>
+  <si>
+    <t>Cascalho</t>
+  </si>
+  <si>
+    <t>Cimento e Argamassa</t>
+  </si>
+  <si>
+    <t>Cimento 50kg</t>
+  </si>
+  <si>
+    <t>Argamassa AC1 20kg</t>
+  </si>
+  <si>
+    <t>Argamassa AC2 20kg</t>
+  </si>
+  <si>
+    <t>Argamassa AC3 20kg</t>
+  </si>
+  <si>
+    <t>Rejunte 1kg</t>
+  </si>
+  <si>
+    <t>Rejunte 5kg</t>
+  </si>
+  <si>
+    <t>Tijolo Baiano</t>
+  </si>
+  <si>
+    <t>Canaleta de Concreto</t>
+  </si>
+  <si>
+    <t>Meio Bloco</t>
+  </si>
+  <si>
+    <t>Barra de Ferro 10mm</t>
+  </si>
+  <si>
+    <t>Barra de Ferro 12mm</t>
+  </si>
+  <si>
+    <t>Arame Recozido 1kg</t>
+  </si>
+  <si>
+    <t>Arame Farpado 500m</t>
+  </si>
+  <si>
+    <t>Tela Soldada</t>
+  </si>
+  <si>
+    <t>Prego 18x27 (kg)</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>Prego 17x21 (kg)</t>
+  </si>
+  <si>
+    <t>Ripa 5m</t>
+  </si>
+  <si>
+    <t>Tábua Pinus 3m</t>
+  </si>
+  <si>
+    <t>Compensado 10mm</t>
+  </si>
+  <si>
+    <t>Compensado 15mm</t>
+  </si>
+  <si>
+    <t>Cobertura</t>
+  </si>
+  <si>
+    <t>Telha Cerâmica</t>
+  </si>
+  <si>
+    <t>Telha Fibrocimento 2,44m</t>
+  </si>
+  <si>
+    <t>Telha Fibrocimento 3,05m</t>
+  </si>
+  <si>
+    <t>Cumeeira Fibrocimento</t>
+  </si>
+  <si>
+    <t>Manta Térmica</t>
+  </si>
+  <si>
+    <t>Prego Telheiro</t>
+  </si>
+  <si>
+    <t>Rodapé Cerâmico</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Gesso 40kg</t>
+  </si>
+  <si>
+    <t>Massa Corrida 25kg</t>
+  </si>
+  <si>
+    <t>Massa Acrílica 25kg</t>
+  </si>
+  <si>
+    <t>Selador 18L</t>
+  </si>
+  <si>
+    <t>Tinta Látex 18L</t>
+  </si>
+  <si>
+    <t>Tinta Acrílica 18L</t>
+  </si>
+  <si>
+    <t>Tinta Esmalte 3,6L</t>
+  </si>
+  <si>
+    <t>Verniz 3,6L</t>
+  </si>
+  <si>
+    <t>Thinner 5L</t>
+  </si>
+  <si>
+    <t>Rolo de Pintura</t>
+  </si>
+  <si>
+    <t>Pincel 2"</t>
+  </si>
+  <si>
+    <t>Bandeja de Pintura</t>
+  </si>
+  <si>
+    <t>Tubo PVC 25mm</t>
+  </si>
+  <si>
+    <t>Registro Esfera</t>
+  </si>
+  <si>
+    <t>Torneira Metal</t>
+  </si>
+  <si>
+    <t>Chuveiro Elétrico</t>
+  </si>
+  <si>
+    <t>Elétrica</t>
+  </si>
+  <si>
+    <t>Fio 2,5mm (100m)</t>
+  </si>
+  <si>
+    <t>Fio 4mm (100m)</t>
+  </si>
+  <si>
+    <t>Disjuntor 20A</t>
+  </si>
+  <si>
+    <t>Tomada Simples</t>
+  </si>
+  <si>
+    <t>Interruptor Simples</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 12W</t>
+  </si>
+  <si>
+    <t>Quadro Distribuição</t>
+  </si>
+  <si>
+    <t>Ferramentas</t>
+  </si>
+  <si>
+    <t>Pá</t>
+  </si>
+  <si>
+    <t>Enxada</t>
+  </si>
+  <si>
+    <t>Colher de Pedreiro</t>
+  </si>
+  <si>
+    <t>Nível 60cm</t>
+  </si>
+  <si>
+    <t>Trena 5m</t>
+  </si>
+  <si>
+    <t>Marreta 2kg</t>
+  </si>
+  <si>
+    <t>Balde 20L</t>
+  </si>
+  <si>
+    <t>Carrinho de Mão</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -171,13 +367,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -490,11 +689,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BA13D2-8BD4-4A6A-90F8-DD922486DCB7}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -521,7 +721,7 @@
       <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>120</v>
       </c>
       <c r="D2" t="s">
@@ -538,7 +738,7 @@
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>115</v>
       </c>
       <c r="D3" t="s">
@@ -553,10 +753,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>140</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="1">
+        <v>135</v>
       </c>
       <c r="D4" t="s">
         <v>22</v>
@@ -570,10 +770,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5">
-        <v>145</v>
+        <v>25</v>
+      </c>
+      <c r="C5" s="1">
+        <v>140</v>
       </c>
       <c r="D5" t="s">
         <v>22</v>
@@ -587,10 +787,10 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6">
-        <v>150</v>
+        <v>26</v>
+      </c>
+      <c r="C6" s="1">
+        <v>145</v>
       </c>
       <c r="D6" t="s">
         <v>22</v>
@@ -601,257 +801,1243 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C7">
-        <v>1.5</v>
+        <v>27</v>
+      </c>
+      <c r="C7" s="1">
+        <v>150</v>
       </c>
       <c r="D7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8">
-        <v>4.5</v>
+        <v>34</v>
+      </c>
+      <c r="C8" s="1">
+        <v>110</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>6.5</v>
+        <v>35</v>
+      </c>
+      <c r="C9" s="1">
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10">
-        <v>28</v>
+        <v>37</v>
+      </c>
+      <c r="C10" s="1">
+        <v>38</v>
       </c>
       <c r="D10" t="s">
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11">
-        <v>65</v>
+        <v>38</v>
+      </c>
+      <c r="C11" s="1">
+        <v>22</v>
       </c>
       <c r="D11" t="s">
         <v>22</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>30</v>
+        <v>39</v>
+      </c>
+      <c r="C12" s="1">
+        <v>28</v>
       </c>
       <c r="D12" t="s">
         <v>22</v>
       </c>
       <c r="E12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13">
-        <v>180</v>
+        <v>40</v>
+      </c>
+      <c r="C13" s="1">
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>22</v>
       </c>
       <c r="E13" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14">
-        <v>220</v>
+        <v>41</v>
+      </c>
+      <c r="C14" s="1">
+        <v>6</v>
       </c>
       <c r="D14" t="s">
         <v>22</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15">
-        <v>95</v>
+        <v>42</v>
+      </c>
+      <c r="C15" s="1">
+        <v>22</v>
       </c>
       <c r="D15" t="s">
         <v>22</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16">
-        <v>28</v>
+        <v>5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>1.5</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E16" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C17">
-        <v>45</v>
+        <v>43</v>
+      </c>
+      <c r="C17" s="1">
+        <v>1.8</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18">
-        <v>22</v>
+        <v>6</v>
+      </c>
+      <c r="C18" s="1">
+        <v>4.5</v>
       </c>
       <c r="D18" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E18" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
-      </c>
-      <c r="C19">
-        <v>85</v>
+        <v>7</v>
+      </c>
+      <c r="C19" s="1">
+        <v>6.5</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20">
-        <v>18</v>
+        <v>44</v>
+      </c>
+      <c r="C20" s="1">
+        <v>7</v>
       </c>
       <c r="D20" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>45</v>
+      </c>
+      <c r="C21" s="1">
+        <v>3.5</v>
+      </c>
+      <c r="D21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>8</v>
+      </c>
+      <c r="B22" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="1">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B23" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="1">
+        <v>45</v>
+      </c>
+      <c r="D23" t="s">
+        <v>22</v>
+      </c>
+      <c r="E23" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="1">
+        <v>65</v>
+      </c>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="1">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>8</v>
+      </c>
+      <c r="B26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C26" s="1">
+        <v>18</v>
+      </c>
+      <c r="D26" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="1">
+        <v>450</v>
+      </c>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>8</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="1">
+        <v>180</v>
+      </c>
+      <c r="D28" t="s">
+        <v>22</v>
+      </c>
+      <c r="E28" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="B29" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="1">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>22</v>
+      </c>
+      <c r="E29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>8</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="C30" s="1">
+        <v>17</v>
+      </c>
+      <c r="D30" t="s">
+        <v>22</v>
+      </c>
+      <c r="E30" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C31" s="1">
+        <v>22</v>
+      </c>
+      <c r="D31" t="s">
+        <v>22</v>
+      </c>
+      <c r="E31" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="1">
+        <v>12</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="1">
+        <v>85</v>
+      </c>
+      <c r="D33" t="s">
+        <v>22</v>
+      </c>
+      <c r="E33" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="1">
+        <v>35</v>
+      </c>
+      <c r="D34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E34" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35" t="s">
+        <v>56</v>
+      </c>
+      <c r="C35" s="1">
+        <v>120</v>
+      </c>
+      <c r="D35" t="s">
+        <v>22</v>
+      </c>
+      <c r="E35" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36" t="s">
+        <v>57</v>
+      </c>
+      <c r="C36" s="1">
+        <v>160</v>
+      </c>
+      <c r="D36" t="s">
+        <v>22</v>
+      </c>
+      <c r="E36" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>58</v>
+      </c>
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="D37" t="s">
+        <v>22</v>
+      </c>
+      <c r="E37" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>58</v>
+      </c>
+      <c r="B38" t="s">
+        <v>60</v>
+      </c>
+      <c r="C38" s="1">
+        <v>55</v>
+      </c>
+      <c r="D38" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" t="s">
+        <v>61</v>
+      </c>
+      <c r="C39" s="1">
+        <v>75</v>
+      </c>
+      <c r="D39" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>58</v>
+      </c>
+      <c r="B40" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="1">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s">
+        <v>22</v>
+      </c>
+      <c r="E40" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>58</v>
+      </c>
+      <c r="B41" t="s">
+        <v>63</v>
+      </c>
+      <c r="C41" s="1">
+        <v>180</v>
+      </c>
+      <c r="D41" t="s">
+        <v>22</v>
+      </c>
+      <c r="E41" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="1">
+        <v>22</v>
+      </c>
+      <c r="D42" t="s">
+        <v>22</v>
+      </c>
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>17</v>
+      </c>
+      <c r="B43" t="s">
+        <v>29</v>
+      </c>
+      <c r="C43" s="1">
+        <v>28</v>
+      </c>
+      <c r="D43" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>17</v>
+      </c>
+      <c r="B44" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="1">
+        <v>65</v>
+      </c>
+      <c r="D44" t="s">
+        <v>22</v>
+      </c>
+      <c r="E44" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C45" s="1">
+        <v>30</v>
+      </c>
+      <c r="D45" t="s">
+        <v>22</v>
+      </c>
+      <c r="E45" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>17</v>
+      </c>
+      <c r="B46" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="1">
+        <v>12</v>
+      </c>
+      <c r="D46" t="s">
+        <v>22</v>
+      </c>
+      <c r="E46" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" t="s">
+        <v>67</v>
+      </c>
+      <c r="C47" s="1">
+        <v>45</v>
+      </c>
+      <c r="D47" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>17</v>
+      </c>
+      <c r="B48" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="1">
+        <v>65</v>
+      </c>
+      <c r="D48" t="s">
+        <v>22</v>
+      </c>
+      <c r="E48" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>17</v>
+      </c>
+      <c r="B49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C49" s="1">
+        <v>85</v>
+      </c>
+      <c r="D49" t="s">
+        <v>22</v>
+      </c>
+      <c r="E49" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>17</v>
+      </c>
+      <c r="B50" t="s">
+        <v>70</v>
+      </c>
+      <c r="C50" s="1">
+        <v>120</v>
+      </c>
+      <c r="D50" t="s">
+        <v>22</v>
+      </c>
+      <c r="E50" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C51" s="1">
+        <v>180</v>
+      </c>
+      <c r="D51" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>18</v>
+      </c>
+      <c r="B52" t="s">
+        <v>72</v>
+      </c>
+      <c r="C52" s="1">
+        <v>220</v>
+      </c>
+      <c r="D52" t="s">
+        <v>22</v>
+      </c>
+      <c r="E52" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>18</v>
+      </c>
+      <c r="B53" t="s">
+        <v>73</v>
+      </c>
+      <c r="C53" s="1">
+        <v>95</v>
+      </c>
+      <c r="D53" t="s">
+        <v>22</v>
+      </c>
+      <c r="E53" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B54" t="s">
+        <v>74</v>
+      </c>
+      <c r="C54" s="1">
+        <v>110</v>
+      </c>
+      <c r="D54" t="s">
+        <v>22</v>
+      </c>
+      <c r="E54" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" t="s">
+        <v>75</v>
+      </c>
+      <c r="C55" s="1">
+        <v>75</v>
+      </c>
+      <c r="D55" t="s">
+        <v>22</v>
+      </c>
+      <c r="E55" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" t="s">
+        <v>76</v>
+      </c>
+      <c r="C56" s="1">
+        <v>18</v>
+      </c>
+      <c r="D56" t="s">
+        <v>22</v>
+      </c>
+      <c r="E56" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>18</v>
+      </c>
+      <c r="B57" t="s">
+        <v>77</v>
+      </c>
+      <c r="C57" s="1">
+        <v>8</v>
+      </c>
+      <c r="D57" t="s">
+        <v>22</v>
+      </c>
+      <c r="E57" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>18</v>
+      </c>
+      <c r="B58" t="s">
+        <v>78</v>
+      </c>
+      <c r="C58" s="1">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>22</v>
+      </c>
+      <c r="E58" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>14</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59" s="1">
+        <v>18</v>
+      </c>
+      <c r="D59" t="s">
+        <v>22</v>
+      </c>
+      <c r="E59" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>14</v>
+      </c>
+      <c r="B60" t="s">
+        <v>79</v>
+      </c>
+      <c r="C60" s="1">
+        <v>22</v>
+      </c>
+      <c r="D60" t="s">
+        <v>22</v>
+      </c>
+      <c r="E60" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>14</v>
+      </c>
+      <c r="B61" t="s">
+        <v>80</v>
+      </c>
+      <c r="C61" s="1">
+        <v>22</v>
+      </c>
+      <c r="D61" t="s">
+        <v>22</v>
+      </c>
+      <c r="E61" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>14</v>
+      </c>
+      <c r="B62" t="s">
         <v>16</v>
       </c>
-      <c r="C21">
+      <c r="C62" s="1">
         <v>320</v>
       </c>
-      <c r="D21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" t="s">
-        <v>29</v>
+      <c r="D62" t="s">
+        <v>22</v>
+      </c>
+      <c r="E62" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>14</v>
+      </c>
+      <c r="B63" t="s">
+        <v>81</v>
+      </c>
+      <c r="C63" s="1">
+        <v>45</v>
+      </c>
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>14</v>
+      </c>
+      <c r="B64" t="s">
+        <v>82</v>
+      </c>
+      <c r="C64" s="1">
+        <v>120</v>
+      </c>
+      <c r="D64" t="s">
+        <v>22</v>
+      </c>
+      <c r="E64" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>83</v>
+      </c>
+      <c r="B65" t="s">
+        <v>84</v>
+      </c>
+      <c r="C65" s="1">
+        <v>180</v>
+      </c>
+      <c r="D65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E65" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>83</v>
+      </c>
+      <c r="B66" t="s">
+        <v>85</v>
+      </c>
+      <c r="C66" s="1">
+        <v>280</v>
+      </c>
+      <c r="D66" t="s">
+        <v>22</v>
+      </c>
+      <c r="E66" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>83</v>
+      </c>
+      <c r="B67" t="s">
+        <v>86</v>
+      </c>
+      <c r="C67" s="1">
+        <v>20</v>
+      </c>
+      <c r="D67" t="s">
+        <v>22</v>
+      </c>
+      <c r="E67" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>83</v>
+      </c>
+      <c r="B68" t="s">
+        <v>87</v>
+      </c>
+      <c r="C68" s="1">
+        <v>8</v>
+      </c>
+      <c r="D68" t="s">
+        <v>22</v>
+      </c>
+      <c r="E68" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>83</v>
+      </c>
+      <c r="B69" t="s">
+        <v>88</v>
+      </c>
+      <c r="C69" s="1">
+        <v>7</v>
+      </c>
+      <c r="D69" t="s">
+        <v>22</v>
+      </c>
+      <c r="E69" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>83</v>
+      </c>
+      <c r="B70" t="s">
+        <v>89</v>
+      </c>
+      <c r="C70" s="1">
+        <v>8</v>
+      </c>
+      <c r="D70" t="s">
+        <v>22</v>
+      </c>
+      <c r="E70" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>83</v>
+      </c>
+      <c r="B71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C71" s="1">
+        <v>85</v>
+      </c>
+      <c r="D71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" t="s">
+        <v>92</v>
+      </c>
+      <c r="C72" s="1">
+        <v>45</v>
+      </c>
+      <c r="D72" t="s">
+        <v>22</v>
+      </c>
+      <c r="E72" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>91</v>
+      </c>
+      <c r="B73" t="s">
+        <v>93</v>
+      </c>
+      <c r="C73" s="1">
+        <v>55</v>
+      </c>
+      <c r="D73" t="s">
+        <v>22</v>
+      </c>
+      <c r="E73" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>91</v>
+      </c>
+      <c r="B74" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="1">
+        <v>25</v>
+      </c>
+      <c r="D74" t="s">
+        <v>22</v>
+      </c>
+      <c r="E74" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>91</v>
+      </c>
+      <c r="B75" t="s">
+        <v>95</v>
+      </c>
+      <c r="C75" s="1">
+        <v>35</v>
+      </c>
+      <c r="D75" t="s">
+        <v>22</v>
+      </c>
+      <c r="E75" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>91</v>
+      </c>
+      <c r="B76" t="s">
+        <v>96</v>
+      </c>
+      <c r="C76" s="1">
+        <v>22</v>
+      </c>
+      <c r="D76" t="s">
+        <v>22</v>
+      </c>
+      <c r="E76" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>91</v>
+      </c>
+      <c r="B77" t="s">
+        <v>97</v>
+      </c>
+      <c r="C77" s="1">
+        <v>65</v>
+      </c>
+      <c r="D77" t="s">
+        <v>22</v>
+      </c>
+      <c r="E77" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" t="s">
+        <v>98</v>
+      </c>
+      <c r="C78" s="1">
+        <v>18</v>
+      </c>
+      <c r="D78" t="s">
+        <v>22</v>
+      </c>
+      <c r="E78" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>91</v>
+      </c>
+      <c r="B79" t="s">
+        <v>99</v>
+      </c>
+      <c r="C79" s="1">
+        <v>280</v>
+      </c>
+      <c r="D79" t="s">
+        <v>22</v>
+      </c>
+      <c r="E79" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>

--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistemas\Pré-Atendimento\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58471B39-7358-43E0-B62D-666381B0F20D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F96AE2-AC8C-4E50-AA9C-8EEC8B8D79DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="91">
   <si>
     <t>nome</t>
   </si>
@@ -36,39 +36,6 @@
     <t>categoria</t>
   </si>
   <si>
-    <t>Agregados</t>
-  </si>
-  <si>
-    <t>Alvenaria</t>
-  </si>
-  <si>
-    <t>Tijolo Cerâmico</t>
-  </si>
-  <si>
-    <t>Bloco de Concreto 14x19x39</t>
-  </si>
-  <si>
-    <t>Bloco Estrutural</t>
-  </si>
-  <si>
-    <t>Ferragens</t>
-  </si>
-  <si>
-    <t>Barra de Ferro 6mm</t>
-  </si>
-  <si>
-    <t>Barra de Ferro 8mm</t>
-  </si>
-  <si>
-    <t>Madeira</t>
-  </si>
-  <si>
-    <t>Caibro 5x6</t>
-  </si>
-  <si>
-    <t>Viga 6m</t>
-  </si>
-  <si>
     <t>Hidráulica</t>
   </si>
   <si>
@@ -78,198 +45,24 @@
     <t>Caixa d'água 500L</t>
   </si>
   <si>
-    <t>Acabamento</t>
-  </si>
-  <si>
-    <t>Tintas</t>
-  </si>
-  <si>
     <t>tipo</t>
   </si>
   <si>
     <t>unidade</t>
   </si>
   <si>
-    <t>Areia Média</t>
-  </si>
-  <si>
     <t>decimal</t>
   </si>
   <si>
-    <t>m³</t>
-  </si>
-  <si>
-    <t>Areia Fina</t>
-  </si>
-  <si>
-    <t>Brita 1</t>
-  </si>
-  <si>
-    <t>Brita 2</t>
-  </si>
-  <si>
-    <t>Pedra Rachão</t>
-  </si>
-  <si>
     <t>un</t>
   </si>
   <si>
-    <t>Piso Cerâmico</t>
-  </si>
-  <si>
-    <t>m²</t>
-  </si>
-  <si>
-    <t>Porcelanato</t>
-  </si>
-  <si>
-    <t>Azulejo</t>
-  </si>
-  <si>
-    <t>Brita 0</t>
-  </si>
-  <si>
-    <t>Pó de Pedra</t>
-  </si>
-  <si>
-    <t>Cascalho</t>
-  </si>
-  <si>
-    <t>Cimento e Argamassa</t>
-  </si>
-  <si>
-    <t>Cimento 50kg</t>
-  </si>
-  <si>
-    <t>Argamassa AC1 20kg</t>
-  </si>
-  <si>
-    <t>Argamassa AC2 20kg</t>
-  </si>
-  <si>
-    <t>Argamassa AC3 20kg</t>
-  </si>
-  <si>
-    <t>Rejunte 1kg</t>
-  </si>
-  <si>
-    <t>Rejunte 5kg</t>
-  </si>
-  <si>
-    <t>Tijolo Baiano</t>
-  </si>
-  <si>
-    <t>Canaleta de Concreto</t>
-  </si>
-  <si>
-    <t>Meio Bloco</t>
-  </si>
-  <si>
-    <t>Barra de Ferro 10mm</t>
-  </si>
-  <si>
-    <t>Barra de Ferro 12mm</t>
-  </si>
-  <si>
-    <t>Arame Recozido 1kg</t>
-  </si>
-  <si>
-    <t>Arame Farpado 500m</t>
-  </si>
-  <si>
-    <t>Tela Soldada</t>
-  </si>
-  <si>
-    <t>Prego 18x27 (kg)</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>Prego 17x21 (kg)</t>
-  </si>
-  <si>
-    <t>Ripa 5m</t>
-  </si>
-  <si>
-    <t>Tábua Pinus 3m</t>
-  </si>
-  <si>
-    <t>Compensado 10mm</t>
-  </si>
-  <si>
-    <t>Compensado 15mm</t>
-  </si>
-  <si>
-    <t>Cobertura</t>
-  </si>
-  <si>
-    <t>Telha Cerâmica</t>
-  </si>
-  <si>
-    <t>Telha Fibrocimento 2,44m</t>
-  </si>
-  <si>
-    <t>Telha Fibrocimento 3,05m</t>
-  </si>
-  <si>
-    <t>Cumeeira Fibrocimento</t>
-  </si>
-  <si>
-    <t>Manta Térmica</t>
-  </si>
-  <si>
-    <t>Prego Telheiro</t>
-  </si>
-  <si>
-    <t>Rodapé Cerâmico</t>
-  </si>
-  <si>
     <t>m</t>
   </si>
   <si>
-    <t>Gesso 40kg</t>
-  </si>
-  <si>
-    <t>Massa Corrida 25kg</t>
-  </si>
-  <si>
-    <t>Massa Acrílica 25kg</t>
-  </si>
-  <si>
-    <t>Selador 18L</t>
-  </si>
-  <si>
-    <t>Tinta Látex 18L</t>
-  </si>
-  <si>
-    <t>Tinta Acrílica 18L</t>
-  </si>
-  <si>
-    <t>Tinta Esmalte 3,6L</t>
-  </si>
-  <si>
-    <t>Verniz 3,6L</t>
-  </si>
-  <si>
-    <t>Thinner 5L</t>
-  </si>
-  <si>
-    <t>Rolo de Pintura</t>
-  </si>
-  <si>
-    <t>Pincel 2"</t>
-  </si>
-  <si>
-    <t>Bandeja de Pintura</t>
-  </si>
-  <si>
     <t>Tubo PVC 25mm</t>
   </si>
   <si>
-    <t>Registro Esfera</t>
-  </si>
-  <si>
     <t>Torneira Metal</t>
   </si>
   <si>
@@ -279,12 +72,6 @@
     <t>Elétrica</t>
   </si>
   <si>
-    <t>Fio 2,5mm (100m)</t>
-  </si>
-  <si>
-    <t>Fio 4mm (100m)</t>
-  </si>
-  <si>
     <t>Disjuntor 20A</t>
   </si>
   <si>
@@ -297,51 +84,227 @@
     <t>Lâmpada LED 12W</t>
   </si>
   <si>
-    <t>Quadro Distribuição</t>
-  </si>
-  <si>
-    <t>Ferramentas</t>
-  </si>
-  <si>
-    <t>Pá</t>
-  </si>
-  <si>
-    <t>Enxada</t>
-  </si>
-  <si>
-    <t>Colher de Pedreiro</t>
-  </si>
-  <si>
-    <t>Nível 60cm</t>
-  </si>
-  <si>
-    <t>Trena 5m</t>
-  </si>
-  <si>
-    <t>Marreta 2kg</t>
-  </si>
-  <si>
-    <t>Balde 20L</t>
-  </si>
-  <si>
-    <t>Carrinho de Mão</t>
+    <t>Tubo PVC 32mm</t>
+  </si>
+  <si>
+    <t>Tubo PVC 40mm</t>
+  </si>
+  <si>
+    <t>Tubo PVC 50mm</t>
+  </si>
+  <si>
+    <t>Joelho 90° 20mm</t>
+  </si>
+  <si>
+    <t>Joelho 90° 25mm</t>
+  </si>
+  <si>
+    <t>Joelho 90° 32mm</t>
+  </si>
+  <si>
+    <t>Tê 20mm</t>
+  </si>
+  <si>
+    <t>Tê 25mm</t>
+  </si>
+  <si>
+    <t>Tê 32mm</t>
+  </si>
+  <si>
+    <t>Registro Esfera 20mm</t>
+  </si>
+  <si>
+    <t>Registro Esfera 25mm</t>
+  </si>
+  <si>
+    <t>Registro Gaveta 25mm</t>
+  </si>
+  <si>
+    <t>Registro Pressão 20mm</t>
+  </si>
+  <si>
+    <t>Adaptador 20mm</t>
+  </si>
+  <si>
+    <t>Adaptador 25mm</t>
+  </si>
+  <si>
+    <t>Luva PVC 20mm</t>
+  </si>
+  <si>
+    <t>Luva PVC 25mm</t>
+  </si>
+  <si>
+    <t>Caixa d'água 1000L</t>
+  </si>
+  <si>
+    <t>Torneira Plástica</t>
+  </si>
+  <si>
+    <t>Chuveiro Simples</t>
+  </si>
+  <si>
+    <t>Sifão Sanfonado</t>
+  </si>
+  <si>
+    <t>Válvula Pia</t>
+  </si>
+  <si>
+    <t>Caixa Sifonada</t>
+  </si>
+  <si>
+    <t>Ralo Simples</t>
+  </si>
+  <si>
+    <t>Ralo Inox</t>
+  </si>
+  <si>
+    <t>Mangueira Jardim 20m</t>
+  </si>
+  <si>
+    <t>Mangueira Jardim 30m</t>
+  </si>
+  <si>
+    <t>Engate Flexível 40cm</t>
+  </si>
+  <si>
+    <t>Engate Flexível 60cm</t>
+  </si>
+  <si>
+    <t>Fita Veda Rosca</t>
+  </si>
+  <si>
+    <t>Cola PVC 175g</t>
+  </si>
+  <si>
+    <t>Cola PVC 850g</t>
+  </si>
+  <si>
+    <t>Caixa de Gordura</t>
+  </si>
+  <si>
+    <t>Caixa de Inspeção</t>
+  </si>
+  <si>
+    <t>Fio 1,5mm (rolo 100m)</t>
+  </si>
+  <si>
+    <t>Fio 2,5mm (rolo 100m)</t>
+  </si>
+  <si>
+    <t>Fio 4mm (rolo 100m)</t>
+  </si>
+  <si>
+    <t>Fio 6mm (rolo 100m)</t>
+  </si>
+  <si>
+    <t>Cabo PP 2x1,5mm</t>
+  </si>
+  <si>
+    <t>Cabo PP 2x2,5mm</t>
+  </si>
+  <si>
+    <t>Disjuntor 10A</t>
+  </si>
+  <si>
+    <t>Disjuntor 16A</t>
+  </si>
+  <si>
+    <t>Disjuntor 32A</t>
+  </si>
+  <si>
+    <t>Disjuntor 50A</t>
+  </si>
+  <si>
+    <t>Quadro de Distribuição 6 disjuntores</t>
+  </si>
+  <si>
+    <t>Quadro de Distribuição 12 disjuntores</t>
+  </si>
+  <si>
+    <t>Tomada Dupla</t>
+  </si>
+  <si>
+    <t>Interruptor Duplo</t>
+  </si>
+  <si>
+    <t>Interruptor Triplo</t>
+  </si>
+  <si>
+    <t>Espelho 1 módulo</t>
+  </si>
+  <si>
+    <t>Espelho 2 módulos</t>
+  </si>
+  <si>
+    <t>Espelho 3 módulos</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 9W</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 15W</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 20W</t>
+  </si>
+  <si>
+    <t>Refletor LED 50W</t>
+  </si>
+  <si>
+    <t>Refletor LED 100W</t>
+  </si>
+  <si>
+    <t>Soquete E27</t>
+  </si>
+  <si>
+    <t>Extensão 5m</t>
+  </si>
+  <si>
+    <t>Extensão 10m</t>
+  </si>
+  <si>
+    <t>Fita Isolante</t>
+  </si>
+  <si>
+    <t>Conector Wago (kit)</t>
+  </si>
+  <si>
+    <t>Caixa de Luz 4x2</t>
+  </si>
+  <si>
+    <t>Caixa de Luz 4x4</t>
+  </si>
+  <si>
+    <t>Eletroduto 20mm</t>
+  </si>
+  <si>
+    <t>Eletroduto 25mm</t>
+  </si>
+  <si>
+    <t>Curva Eletroduto</t>
+  </si>
+  <si>
+    <t>Abraçadeira Nylon (100un)</t>
+  </si>
+  <si>
+    <t>Relé Fotocélula</t>
+  </si>
+  <si>
+    <t>Campainha Residencial</t>
+  </si>
+  <si>
+    <t>Transformador 127/220</t>
+  </si>
+  <si>
+    <t>int</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-  </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -367,16 +330,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Moeda" xfId="1" builtinId="4"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -689,7 +649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BA13D2-8BD4-4A6A-90F8-DD922486DCB7}">
-  <dimension ref="A1:E79"/>
+  <dimension ref="A1:E81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -708,10 +668,10 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="E1" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -719,16 +679,16 @@
         <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="1">
-        <v>120</v>
+        <v>4</v>
+      </c>
+      <c r="C2">
+        <v>18</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -736,16 +696,16 @@
         <v>3</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="1">
-        <v>115</v>
+        <v>11</v>
+      </c>
+      <c r="C3">
+        <v>22</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -753,16 +713,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C4" s="1">
-        <v>135</v>
+        <v>19</v>
+      </c>
+      <c r="C4">
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -770,16 +730,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="1">
-        <v>140</v>
+        <v>20</v>
+      </c>
+      <c r="C5">
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -787,16 +747,16 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="1">
-        <v>145</v>
+        <v>21</v>
+      </c>
+      <c r="C6">
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -804,16 +764,16 @@
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1">
-        <v>150</v>
+        <v>22</v>
+      </c>
+      <c r="C7">
+        <v>2.5</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -821,16 +781,16 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="1">
-        <v>110</v>
+        <v>23</v>
+      </c>
+      <c r="C8">
+        <v>3.5</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
@@ -838,849 +798,849 @@
         <v>3</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="1">
-        <v>100</v>
+        <v>24</v>
+      </c>
+      <c r="C9">
+        <v>4.5</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="1">
-        <v>38</v>
+        <v>25</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="1">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="C11">
+        <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="1">
-        <v>28</v>
+        <v>27</v>
+      </c>
+      <c r="C12">
+        <v>5.5</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="1">
-        <v>35</v>
+        <v>28</v>
+      </c>
+      <c r="C13">
+        <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="1">
-        <v>6</v>
+        <v>29</v>
+      </c>
+      <c r="C14">
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="1">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="C15">
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C16" s="1">
-        <v>1.5</v>
+        <v>31</v>
+      </c>
+      <c r="C16">
+        <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="1">
-        <v>1.8</v>
+        <v>32</v>
+      </c>
+      <c r="C17">
+        <v>2</v>
       </c>
       <c r="D17" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="1">
-        <v>4.5</v>
+        <v>33</v>
+      </c>
+      <c r="C18">
+        <v>2.5</v>
       </c>
       <c r="D18" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="1">
-        <v>6.5</v>
+        <v>34</v>
+      </c>
+      <c r="C19">
+        <v>1.8</v>
       </c>
       <c r="D19" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
-      </c>
-      <c r="C20" s="1">
-        <v>7</v>
+        <v>35</v>
+      </c>
+      <c r="C20">
+        <v>2.5</v>
       </c>
       <c r="D20" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C21" s="1">
-        <v>3.5</v>
+        <v>5</v>
+      </c>
+      <c r="C21">
+        <v>320</v>
       </c>
       <c r="D21" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="1">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="C22">
+        <v>580</v>
       </c>
       <c r="D22" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="1">
-        <v>45</v>
+        <v>37</v>
+      </c>
+      <c r="C23">
+        <v>15</v>
       </c>
       <c r="D23" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E23" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="1">
-        <v>65</v>
+        <v>12</v>
+      </c>
+      <c r="C24">
+        <v>45</v>
       </c>
       <c r="D24" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E24" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C25" s="1">
-        <v>85</v>
+        <v>38</v>
+      </c>
+      <c r="C25">
+        <v>35</v>
       </c>
       <c r="D25" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="1">
-        <v>18</v>
+        <v>13</v>
+      </c>
+      <c r="C26">
+        <v>120</v>
       </c>
       <c r="D26" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
-      </c>
-      <c r="C27" s="1">
-        <v>450</v>
+        <v>39</v>
+      </c>
+      <c r="C27">
+        <v>12</v>
       </c>
       <c r="D27" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="1">
-        <v>180</v>
+        <v>40</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E28" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B29" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="1">
-        <v>18</v>
+        <v>41</v>
+      </c>
+      <c r="C29">
+        <v>25</v>
       </c>
       <c r="D29" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E29" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30">
         <v>8</v>
       </c>
-      <c r="B30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" s="1">
-        <v>17</v>
-      </c>
       <c r="D30" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E30" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C31" s="1">
-        <v>22</v>
+        <v>43</v>
+      </c>
+      <c r="C31">
+        <v>25</v>
       </c>
       <c r="D31" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E31" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="1">
-        <v>12</v>
+        <v>44</v>
+      </c>
+      <c r="C32">
+        <v>65</v>
       </c>
       <c r="D32" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E32" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B33" t="s">
-        <v>13</v>
-      </c>
-      <c r="C33" s="1">
+        <v>45</v>
+      </c>
+      <c r="C33">
         <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E33" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C34" s="1">
-        <v>35</v>
+        <v>46</v>
+      </c>
+      <c r="C34">
+        <v>12</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E34" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
-      </c>
-      <c r="C35" s="1">
-        <v>120</v>
+        <v>47</v>
+      </c>
+      <c r="C35">
+        <v>15</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E35" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
-      </c>
-      <c r="C36" s="1">
-        <v>160</v>
+        <v>48</v>
+      </c>
+      <c r="C36">
+        <v>5</v>
       </c>
       <c r="D36" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E36" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
-      </c>
-      <c r="C37" s="1">
-        <v>2.8</v>
+        <v>49</v>
+      </c>
+      <c r="C37">
+        <v>18</v>
       </c>
       <c r="D37" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E37" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B38" t="s">
-        <v>60</v>
-      </c>
-      <c r="C38" s="1">
-        <v>55</v>
+        <v>50</v>
+      </c>
+      <c r="C38">
+        <v>45</v>
       </c>
       <c r="D38" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E38" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
-      </c>
-      <c r="C39" s="1">
-        <v>75</v>
+        <v>51</v>
+      </c>
+      <c r="C39">
+        <v>120</v>
       </c>
       <c r="D39" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E39" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>58</v>
+        <v>3</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
-      </c>
-      <c r="C40" s="1">
-        <v>35</v>
+        <v>52</v>
+      </c>
+      <c r="C40">
+        <v>95</v>
       </c>
       <c r="D40" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E40" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C41" s="1">
-        <v>180</v>
+        <v>53</v>
+      </c>
+      <c r="C41">
+        <v>120</v>
       </c>
       <c r="D41" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E41" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>64</v>
-      </c>
-      <c r="C42" s="1">
-        <v>22</v>
+        <v>54</v>
+      </c>
+      <c r="C42">
+        <v>180</v>
       </c>
       <c r="D42" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E42" t="s">
-        <v>52</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43" s="1">
-        <v>28</v>
+        <v>55</v>
+      </c>
+      <c r="C43">
+        <v>280</v>
       </c>
       <c r="D43" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E43" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="1">
-        <v>65</v>
+        <v>56</v>
+      </c>
+      <c r="C44">
+        <v>420</v>
       </c>
       <c r="D44" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E44" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C45" s="1">
-        <v>30</v>
+        <v>57</v>
+      </c>
+      <c r="C45">
+        <v>6</v>
       </c>
       <c r="D45" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E45" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="1">
-        <v>12</v>
+        <v>58</v>
+      </c>
+      <c r="C46">
+        <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="E46" t="s">
-        <v>66</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>67</v>
-      </c>
-      <c r="C47" s="1">
-        <v>45</v>
+        <v>59</v>
+      </c>
+      <c r="C47">
+        <v>18</v>
       </c>
       <c r="D47" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E47" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
-      </c>
-      <c r="C48" s="1">
-        <v>65</v>
+        <v>60</v>
+      </c>
+      <c r="C48">
+        <v>18</v>
       </c>
       <c r="D48" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E48" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="1">
-        <v>85</v>
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>20</v>
       </c>
       <c r="D49" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E49" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
-      </c>
-      <c r="C50" s="1">
-        <v>120</v>
+        <v>61</v>
+      </c>
+      <c r="C50">
+        <v>25</v>
       </c>
       <c r="D50" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E50" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
-      </c>
-      <c r="C51" s="1">
-        <v>180</v>
+        <v>62</v>
+      </c>
+      <c r="C51">
+        <v>35</v>
       </c>
       <c r="D51" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E51" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B52" t="s">
-        <v>72</v>
-      </c>
-      <c r="C52" s="1">
-        <v>220</v>
+        <v>63</v>
+      </c>
+      <c r="C52">
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E52" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
-      </c>
-      <c r="C53" s="1">
-        <v>95</v>
+        <v>64</v>
+      </c>
+      <c r="C53">
+        <v>140</v>
       </c>
       <c r="D53" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E53" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B54" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="1">
-        <v>110</v>
+        <v>16</v>
+      </c>
+      <c r="C54">
+        <v>8</v>
       </c>
       <c r="D54" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E54" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B55" t="s">
-        <v>75</v>
-      </c>
-      <c r="C55" s="1">
-        <v>75</v>
+        <v>65</v>
+      </c>
+      <c r="C55">
+        <v>12</v>
       </c>
       <c r="D55" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E55" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B56" t="s">
-        <v>76</v>
-      </c>
-      <c r="C56" s="1">
-        <v>18</v>
+        <v>17</v>
+      </c>
+      <c r="C56">
+        <v>7</v>
       </c>
       <c r="D56" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E56" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B57" t="s">
-        <v>77</v>
-      </c>
-      <c r="C57" s="1">
-        <v>8</v>
+        <v>66</v>
+      </c>
+      <c r="C57">
+        <v>10</v>
       </c>
       <c r="D57" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E57" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B58" t="s">
-        <v>78</v>
-      </c>
-      <c r="C58" s="1">
-        <v>15</v>
+        <v>67</v>
+      </c>
+      <c r="C58">
+        <v>14</v>
       </c>
       <c r="D58" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E58" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1688,16 +1648,16 @@
         <v>14</v>
       </c>
       <c r="B59" t="s">
-        <v>15</v>
-      </c>
-      <c r="C59" s="1">
-        <v>18</v>
+        <v>68</v>
+      </c>
+      <c r="C59">
+        <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E59" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -1705,16 +1665,16 @@
         <v>14</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
-      </c>
-      <c r="C60" s="1">
-        <v>22</v>
+        <v>69</v>
+      </c>
+      <c r="C60">
+        <v>5</v>
       </c>
       <c r="D60" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E60" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -1722,16 +1682,16 @@
         <v>14</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
-      </c>
-      <c r="C61" s="1">
-        <v>22</v>
+        <v>70</v>
+      </c>
+      <c r="C61">
+        <v>7</v>
       </c>
       <c r="D61" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E61" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -1739,16 +1699,16 @@
         <v>14</v>
       </c>
       <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" s="1">
-        <v>320</v>
+        <v>71</v>
+      </c>
+      <c r="C62">
+        <v>6</v>
       </c>
       <c r="D62" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E62" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -1756,16 +1716,16 @@
         <v>14</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
-      </c>
-      <c r="C63" s="1">
-        <v>45</v>
+        <v>18</v>
+      </c>
+      <c r="C63">
+        <v>8</v>
       </c>
       <c r="D63" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E63" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -1773,271 +1733,305 @@
         <v>14</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
-      </c>
-      <c r="C64" s="1">
-        <v>120</v>
+        <v>72</v>
+      </c>
+      <c r="C64">
+        <v>10</v>
       </c>
       <c r="D64" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E64" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B65" t="s">
-        <v>84</v>
-      </c>
-      <c r="C65" s="1">
-        <v>180</v>
+        <v>73</v>
+      </c>
+      <c r="C65">
+        <v>15</v>
       </c>
       <c r="D65" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E65" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B66" t="s">
-        <v>85</v>
-      </c>
-      <c r="C66" s="1">
-        <v>280</v>
+        <v>74</v>
+      </c>
+      <c r="C66">
+        <v>65</v>
       </c>
       <c r="D66" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E66" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
-      </c>
-      <c r="C67" s="1">
-        <v>20</v>
+        <v>75</v>
+      </c>
+      <c r="C67">
+        <v>120</v>
       </c>
       <c r="D67" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E67" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B68" t="s">
-        <v>87</v>
-      </c>
-      <c r="C68" s="1">
-        <v>8</v>
+        <v>76</v>
+      </c>
+      <c r="C68">
+        <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E68" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B69" t="s">
-        <v>88</v>
-      </c>
-      <c r="C69" s="1">
-        <v>7</v>
+        <v>77</v>
+      </c>
+      <c r="C69">
+        <v>25</v>
       </c>
       <c r="D69" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E69" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B70" t="s">
-        <v>89</v>
-      </c>
-      <c r="C70" s="1">
-        <v>8</v>
+        <v>78</v>
+      </c>
+      <c r="C70">
+        <v>45</v>
       </c>
       <c r="D70" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E70" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>83</v>
+        <v>14</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
-      </c>
-      <c r="C71" s="1">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="C71">
+        <v>6</v>
       </c>
       <c r="D71" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E71" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B72" t="s">
-        <v>92</v>
-      </c>
-      <c r="C72" s="1">
-        <v>45</v>
+        <v>80</v>
+      </c>
+      <c r="C72">
+        <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E72" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B73" t="s">
-        <v>93</v>
-      </c>
-      <c r="C73" s="1">
-        <v>55</v>
+        <v>81</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E73" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B74" t="s">
-        <v>94</v>
-      </c>
-      <c r="C74" s="1">
-        <v>25</v>
+        <v>82</v>
+      </c>
+      <c r="C74">
+        <v>5</v>
       </c>
       <c r="D74" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E74" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B75" t="s">
-        <v>95</v>
-      </c>
-      <c r="C75" s="1">
-        <v>35</v>
+        <v>83</v>
+      </c>
+      <c r="C75">
+        <v>12</v>
       </c>
       <c r="D75" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E75" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
-      </c>
-      <c r="C76" s="1">
-        <v>22</v>
+        <v>84</v>
+      </c>
+      <c r="C76">
+        <v>15</v>
       </c>
       <c r="D76" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E76" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B77" t="s">
-        <v>97</v>
-      </c>
-      <c r="C77" s="1">
-        <v>65</v>
+        <v>85</v>
+      </c>
+      <c r="C77">
+        <v>4</v>
       </c>
       <c r="D77" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E77" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B78" t="s">
-        <v>98</v>
-      </c>
-      <c r="C78" s="1">
+        <v>86</v>
+      </c>
+      <c r="C78">
         <v>18</v>
       </c>
       <c r="D78" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E78" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>91</v>
+        <v>14</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
-      </c>
-      <c r="C79" s="1">
-        <v>280</v>
+        <v>87</v>
+      </c>
+      <c r="C79">
+        <v>35</v>
       </c>
       <c r="D79" t="s">
-        <v>22</v>
+        <v>90</v>
       </c>
       <c r="E79" t="s">
-        <v>28</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>14</v>
+      </c>
+      <c r="B80" t="s">
+        <v>88</v>
+      </c>
+      <c r="C80">
+        <v>45</v>
+      </c>
+      <c r="D80" t="s">
+        <v>90</v>
+      </c>
+      <c r="E80" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>14</v>
+      </c>
+      <c r="B81" t="s">
+        <v>89</v>
+      </c>
+      <c r="C81">
+        <v>120</v>
+      </c>
+      <c r="D81" t="s">
+        <v>90</v>
+      </c>
+      <c r="E81" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistemas\Pré-Atendimento\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F96AE2-AC8C-4E50-AA9C-8EEC8B8D79DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899DD3AC-58F3-48AE-B405-96445126F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="113">
   <si>
     <t>nome</t>
   </si>
@@ -36,268 +36,334 @@
     <t>categoria</t>
   </si>
   <si>
-    <t>Hidráulica</t>
-  </si>
-  <si>
-    <t>Tubo PVC 20mm</t>
-  </si>
-  <si>
-    <t>Caixa d'água 500L</t>
-  </si>
-  <si>
     <t>tipo</t>
   </si>
   <si>
     <t>unidade</t>
   </si>
   <si>
-    <t>decimal</t>
-  </si>
-  <si>
     <t>un</t>
   </si>
   <si>
-    <t>m</t>
-  </si>
-  <si>
-    <t>Tubo PVC 25mm</t>
-  </si>
-  <si>
-    <t>Torneira Metal</t>
-  </si>
-  <si>
-    <t>Chuveiro Elétrico</t>
-  </si>
-  <si>
-    <t>Elétrica</t>
-  </si>
-  <si>
-    <t>Disjuntor 20A</t>
-  </si>
-  <si>
-    <t>Tomada Simples</t>
-  </si>
-  <si>
-    <t>Interruptor Simples</t>
-  </si>
-  <si>
-    <t>Lâmpada LED 12W</t>
-  </si>
-  <si>
-    <t>Tubo PVC 32mm</t>
-  </si>
-  <si>
-    <t>Tubo PVC 40mm</t>
-  </si>
-  <si>
-    <t>Tubo PVC 50mm</t>
-  </si>
-  <si>
-    <t>Joelho 90° 20mm</t>
-  </si>
-  <si>
-    <t>Joelho 90° 25mm</t>
-  </si>
-  <si>
-    <t>Joelho 90° 32mm</t>
-  </si>
-  <si>
-    <t>Tê 20mm</t>
-  </si>
-  <si>
-    <t>Tê 25mm</t>
-  </si>
-  <si>
-    <t>Tê 32mm</t>
-  </si>
-  <si>
-    <t>Registro Esfera 20mm</t>
-  </si>
-  <si>
-    <t>Registro Esfera 25mm</t>
-  </si>
-  <si>
-    <t>Registro Gaveta 25mm</t>
-  </si>
-  <si>
-    <t>Registro Pressão 20mm</t>
-  </si>
-  <si>
-    <t>Adaptador 20mm</t>
-  </si>
-  <si>
-    <t>Adaptador 25mm</t>
-  </si>
-  <si>
-    <t>Luva PVC 20mm</t>
-  </si>
-  <si>
-    <t>Luva PVC 25mm</t>
-  </si>
-  <si>
-    <t>Caixa d'água 1000L</t>
-  </si>
-  <si>
-    <t>Torneira Plástica</t>
-  </si>
-  <si>
-    <t>Chuveiro Simples</t>
-  </si>
-  <si>
-    <t>Sifão Sanfonado</t>
-  </si>
-  <si>
-    <t>Válvula Pia</t>
-  </si>
-  <si>
-    <t>Caixa Sifonada</t>
-  </si>
-  <si>
-    <t>Ralo Simples</t>
-  </si>
-  <si>
-    <t>Ralo Inox</t>
-  </si>
-  <si>
-    <t>Mangueira Jardim 20m</t>
-  </si>
-  <si>
-    <t>Mangueira Jardim 30m</t>
-  </si>
-  <si>
-    <t>Engate Flexível 40cm</t>
-  </si>
-  <si>
-    <t>Engate Flexível 60cm</t>
-  </si>
-  <si>
-    <t>Fita Veda Rosca</t>
-  </si>
-  <si>
-    <t>Cola PVC 175g</t>
-  </si>
-  <si>
-    <t>Cola PVC 850g</t>
-  </si>
-  <si>
-    <t>Caixa de Gordura</t>
-  </si>
-  <si>
-    <t>Caixa de Inspeção</t>
-  </si>
-  <si>
-    <t>Fio 1,5mm (rolo 100m)</t>
-  </si>
-  <si>
-    <t>Fio 2,5mm (rolo 100m)</t>
-  </si>
-  <si>
-    <t>Fio 4mm (rolo 100m)</t>
-  </si>
-  <si>
-    <t>Fio 6mm (rolo 100m)</t>
-  </si>
-  <si>
-    <t>Cabo PP 2x1,5mm</t>
-  </si>
-  <si>
-    <t>Cabo PP 2x2,5mm</t>
-  </si>
-  <si>
-    <t>Disjuntor 10A</t>
-  </si>
-  <si>
-    <t>Disjuntor 16A</t>
-  </si>
-  <si>
-    <t>Disjuntor 32A</t>
-  </si>
-  <si>
-    <t>Disjuntor 50A</t>
-  </si>
-  <si>
-    <t>Quadro de Distribuição 6 disjuntores</t>
-  </si>
-  <si>
-    <t>Quadro de Distribuição 12 disjuntores</t>
-  </si>
-  <si>
-    <t>Tomada Dupla</t>
-  </si>
-  <si>
-    <t>Interruptor Duplo</t>
-  </si>
-  <si>
-    <t>Interruptor Triplo</t>
-  </si>
-  <si>
-    <t>Espelho 1 módulo</t>
-  </si>
-  <si>
-    <t>Espelho 2 módulos</t>
-  </si>
-  <si>
-    <t>Espelho 3 módulos</t>
-  </si>
-  <si>
-    <t>Lâmpada LED 9W</t>
-  </si>
-  <si>
-    <t>Lâmpada LED 15W</t>
-  </si>
-  <si>
-    <t>Lâmpada LED 20W</t>
-  </si>
-  <si>
-    <t>Refletor LED 50W</t>
-  </si>
-  <si>
-    <t>Refletor LED 100W</t>
-  </si>
-  <si>
-    <t>Soquete E27</t>
-  </si>
-  <si>
-    <t>Extensão 5m</t>
-  </si>
-  <si>
-    <t>Extensão 10m</t>
-  </si>
-  <si>
-    <t>Fita Isolante</t>
-  </si>
-  <si>
-    <t>Conector Wago (kit)</t>
-  </si>
-  <si>
-    <t>Caixa de Luz 4x2</t>
-  </si>
-  <si>
-    <t>Caixa de Luz 4x4</t>
-  </si>
-  <si>
-    <t>Eletroduto 20mm</t>
-  </si>
-  <si>
-    <t>Eletroduto 25mm</t>
-  </si>
-  <si>
-    <t>Curva Eletroduto</t>
-  </si>
-  <si>
-    <t>Abraçadeira Nylon (100un)</t>
-  </si>
-  <si>
-    <t>Relé Fotocélula</t>
-  </si>
-  <si>
-    <t>Campainha Residencial</t>
-  </si>
-  <si>
-    <t>Transformador 127/220</t>
-  </si>
-  <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>Perfumaria</t>
+  </si>
+  <si>
+    <t>Kaiak Masculino 100ml</t>
+  </si>
+  <si>
+    <t>Kaiak Aventura 100ml</t>
+  </si>
+  <si>
+    <t>Essencial Masculino 100ml</t>
+  </si>
+  <si>
+    <t>Essencial Oud 100ml</t>
+  </si>
+  <si>
+    <t>Luna Feminino 75ml</t>
+  </si>
+  <si>
+    <t>Ilía Feminino 75ml</t>
+  </si>
+  <si>
+    <t>Ekos Frescor Maracujá 150ml</t>
+  </si>
+  <si>
+    <t>Ekos Frescor Açaí 150ml</t>
+  </si>
+  <si>
+    <t>Humor Próprio 75ml</t>
+  </si>
+  <si>
+    <t>Humor a Dois 75ml</t>
+  </si>
+  <si>
+    <t>Kriska Feminino 100ml</t>
+  </si>
+  <si>
+    <t>Kriska Drama 100ml</t>
+  </si>
+  <si>
+    <t>Biografia Masculino 100ml</t>
+  </si>
+  <si>
+    <t>Biografia Feminino 100ml</t>
+  </si>
+  <si>
+    <t>Kaiak Urbe 100ml</t>
+  </si>
+  <si>
+    <t>Kaiak Aero 100ml</t>
+  </si>
+  <si>
+    <t>Ilía Secreto 75ml</t>
+  </si>
+  <si>
+    <t>Luna Absoluta 75ml</t>
+  </si>
+  <si>
+    <t>Essencial Exclusivo 100ml</t>
+  </si>
+  <si>
+    <t>Kaiak Oceano 100ml</t>
+  </si>
+  <si>
+    <t>Corpo</t>
+  </si>
+  <si>
+    <t>Hidratante Tododia Ameixa 400ml</t>
+  </si>
+  <si>
+    <t>Hidratante Tododia Macadâmia 400ml</t>
+  </si>
+  <si>
+    <t>Hidratante Tododia Algodão 400ml</t>
+  </si>
+  <si>
+    <t>Hidratante Tododia Manga Rosa 400ml</t>
+  </si>
+  <si>
+    <t>Hidratante Tododia Framboesa 400ml</t>
+  </si>
+  <si>
+    <t>Sabonete Barra Tododia (5un)</t>
+  </si>
+  <si>
+    <t>Sabonete Líquido Tododia 300ml</t>
+  </si>
+  <si>
+    <t>Óleo Corporal Sève Amêndoas 200ml</t>
+  </si>
+  <si>
+    <t>Óleo Corporal Sève Flor de Laranjeira</t>
+  </si>
+  <si>
+    <t>Creme para Mãos Tododia 50ml</t>
+  </si>
+  <si>
+    <t>Desodorante Roll-on Tododia</t>
+  </si>
+  <si>
+    <t>Body Splash Tododia Ameixa</t>
+  </si>
+  <si>
+    <t>Body Splash Tododia Macadâmia</t>
+  </si>
+  <si>
+    <t>Esfoliante Corporal Tododia</t>
+  </si>
+  <si>
+    <t>Hidratante Ekos Castanha 400ml</t>
+  </si>
+  <si>
+    <t>Hidratante Ekos Açaí 400ml</t>
+  </si>
+  <si>
+    <t>Polpa Hidratante Castanha 75g</t>
+  </si>
+  <si>
+    <t>Polpa Hidratante Açaí 75g</t>
+  </si>
+  <si>
+    <t>Sabonete Ekos (3un)</t>
+  </si>
+  <si>
+    <t>Óleo Trifásico Maracujá</t>
+  </si>
+  <si>
+    <t>Creme Firmador Corpo</t>
+  </si>
+  <si>
+    <t>Creme Antiestrias</t>
+  </si>
+  <si>
+    <t>Desodorante Spray</t>
+  </si>
+  <si>
+    <t>Sabonete Líquido Ekos 250ml</t>
+  </si>
+  <si>
+    <t>Kit Hidratante Tododia</t>
+  </si>
+  <si>
+    <t>Cabelos</t>
+  </si>
+  <si>
+    <t>Shampoo Lumina Hidratação 300ml</t>
+  </si>
+  <si>
+    <t>Condicionador Lumina Hidratação 300ml</t>
+  </si>
+  <si>
+    <t>Máscara Lumina 250g</t>
+  </si>
+  <si>
+    <t>Shampoo Lumina Nutrição 300ml</t>
+  </si>
+  <si>
+    <t>Condicionador Lumina Nutrição</t>
+  </si>
+  <si>
+    <t>Shampoo Lumina Reconstrução</t>
+  </si>
+  <si>
+    <t>Condicionador Reconstrução</t>
+  </si>
+  <si>
+    <t>Óleo Capilar Lumina</t>
+  </si>
+  <si>
+    <t>Leave-in Lumina</t>
+  </si>
+  <si>
+    <t>Ampola Capilar Lumina</t>
+  </si>
+  <si>
+    <t>Shampoo Anticaspa</t>
+  </si>
+  <si>
+    <t>Condicionador Anticaspa</t>
+  </si>
+  <si>
+    <t>Máscara Reparadora</t>
+  </si>
+  <si>
+    <t>Creme Pentear Cachos</t>
+  </si>
+  <si>
+    <t>Ativador de Cachos</t>
+  </si>
+  <si>
+    <t>Spray Finalizador</t>
+  </si>
+  <si>
+    <t>Shampoo Infantil</t>
+  </si>
+  <si>
+    <t>Condicionador Infantil</t>
+  </si>
+  <si>
+    <t>Kit Cabelos Lumina</t>
+  </si>
+  <si>
+    <t>Tônico Capilar</t>
+  </si>
+  <si>
+    <t>Rosto</t>
+  </si>
+  <si>
+    <t>Gel Limpeza Chronos</t>
+  </si>
+  <si>
+    <t>Hidratante Chronos</t>
+  </si>
+  <si>
+    <t>Sérum Antissinais</t>
+  </si>
+  <si>
+    <t>Protetor Solar FPS50</t>
+  </si>
+  <si>
+    <t>Protetor FPS30</t>
+  </si>
+  <si>
+    <t>Sabonete Facial</t>
+  </si>
+  <si>
+    <t>Tônico Facial</t>
+  </si>
+  <si>
+    <t>Creme Área Olhos</t>
+  </si>
+  <si>
+    <t>Máscara Facial</t>
+  </si>
+  <si>
+    <t>Esfoliante Facial</t>
+  </si>
+  <si>
+    <t>Água Micelar</t>
+  </si>
+  <si>
+    <t>Kit Rosto Chronos</t>
+  </si>
+  <si>
+    <t>Creme Noturno</t>
+  </si>
+  <si>
+    <t>Creme Diurno</t>
+  </si>
+  <si>
+    <t>Sérum Vitamina C</t>
+  </si>
+  <si>
+    <t>Maquiagem</t>
+  </si>
+  <si>
+    <t>Base Una</t>
+  </si>
+  <si>
+    <t>Batom Matte</t>
+  </si>
+  <si>
+    <t>Máscara Cílios</t>
+  </si>
+  <si>
+    <t>Pó Compacto</t>
+  </si>
+  <si>
+    <t>Corretivo</t>
+  </si>
+  <si>
+    <t>Blush</t>
+  </si>
+  <si>
+    <t>Iluminador</t>
+  </si>
+  <si>
+    <t>Paleta Sombras</t>
+  </si>
+  <si>
+    <t>Delineador</t>
+  </si>
+  <si>
+    <t>Kit Maquiagem</t>
+  </si>
+  <si>
+    <t>Infantil</t>
+  </si>
+  <si>
+    <t>Colônia Mamãe e Bebê</t>
+  </si>
+  <si>
+    <t>Sabonete Líquido Bebê</t>
+  </si>
+  <si>
+    <t>Hidratante Bebê</t>
+  </si>
+  <si>
+    <t>Óleo Bebê</t>
+  </si>
+  <si>
+    <t>Shampoo Bebê</t>
+  </si>
+  <si>
+    <t>Condicionador Bebê</t>
+  </si>
+  <si>
+    <t>Lenço Umedecido</t>
+  </si>
+  <si>
+    <t>Kit Bebê Completo</t>
+  </si>
+  <si>
+    <t>Colônia Infantil</t>
+  </si>
+  <si>
+    <t>Sabonete Barra Bebê</t>
   </si>
 </sst>
 </file>
@@ -649,7 +715,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BA13D2-8BD4-4A6A-90F8-DD922486DCB7}">
-  <dimension ref="A1:E81"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -668,1370 +734,1710 @@
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2">
-        <v>18</v>
+        <v>130</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>22</v>
+        <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C4">
-        <v>28</v>
+        <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C5">
-        <v>35</v>
+        <v>180</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>48</v>
+        <v>140</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C7">
-        <v>2.5</v>
+        <v>130</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C8">
-        <v>3.5</v>
+        <v>120</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C9">
-        <v>4.5</v>
+        <v>120</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C12">
-        <v>5.5</v>
+        <v>95</v>
       </c>
       <c r="D12" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="C13">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="D13" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C14">
-        <v>22</v>
+        <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="C15">
-        <v>35</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C16">
-        <v>28</v>
+        <v>140</v>
       </c>
       <c r="D16" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C17">
-        <v>2</v>
+        <v>145</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C18">
-        <v>2.5</v>
+        <v>135</v>
       </c>
       <c r="D18" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="C19">
-        <v>1.8</v>
+        <v>150</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C20">
-        <v>2.5</v>
+        <v>190</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="C21">
-        <v>320</v>
+        <v>150</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C22">
-        <v>580</v>
+        <v>40</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C23">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B24" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C24">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C25">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B26" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C26">
-        <v>120</v>
+        <v>42</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C27">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C28">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C29">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C30">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="D30" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B31" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C31">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="D31" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B32" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C32">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="D32" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B33" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33">
         <v>45</v>
       </c>
-      <c r="C33">
-        <v>85</v>
-      </c>
       <c r="D33" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C34">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D34" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C35">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="D35" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C36">
-        <v>5</v>
+        <v>55</v>
       </c>
       <c r="D36" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C37">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D37" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E37" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B38" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C38">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="D38" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B39" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C39">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D39" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="B40" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C40">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="D40" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B41" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C41">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E41" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B42" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C42">
-        <v>180</v>
+        <v>80</v>
       </c>
       <c r="D42" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E42" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C43">
-        <v>280</v>
+        <v>85</v>
       </c>
       <c r="D43" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E43" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C44">
-        <v>420</v>
+        <v>22</v>
       </c>
       <c r="D44" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E44" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B45" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C45">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D45" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E45" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B46" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C46">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="D46" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E46" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B47" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C47">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D47" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E47" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C48">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="D48" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E48" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B49" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="C49">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D49" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B50" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C50">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="D50" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E50" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B51" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C51">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="D51" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E51" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B52" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C52">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="D52" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E52" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C53">
-        <v>140</v>
+        <v>34</v>
       </c>
       <c r="D53" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E53" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B54" t="s">
-        <v>16</v>
+        <v>62</v>
       </c>
       <c r="C54">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="D54" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E54" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C55">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="D55" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E55" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
       <c r="C56">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D56" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E56" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C57">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D57" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E57" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B58" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C58">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D58" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E58" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B59" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59">
-        <v>3</v>
+        <v>55</v>
       </c>
       <c r="D59" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B60" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C60">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="D60" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C61">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D61" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B62" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C62">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D62" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B63" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="C63">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D63" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E63" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B64" t="s">
         <v>72</v>
       </c>
       <c r="C64">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="D64" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E64" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B65" t="s">
         <v>73</v>
       </c>
       <c r="C65">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>14</v>
+        <v>54</v>
       </c>
       <c r="B66" t="s">
         <v>74</v>
       </c>
       <c r="C66">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="D66" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E66" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C67">
-        <v>120</v>
+        <v>46</v>
       </c>
       <c r="D67" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E67" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B68" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C68">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="D68" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E68" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C69">
-        <v>25</v>
+        <v>120</v>
       </c>
       <c r="D69" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E69" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B70" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C70">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D70" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E70" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C71">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="D71" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E71" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B72" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C72">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="D72" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E72" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C73">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D73" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E73" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B74" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C74">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="D74" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E74" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B75" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C75">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="D75" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E75" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B76" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C76">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="D76" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E76" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C77">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="D77" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E77" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B78" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C78">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="D78" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E78" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B79" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C79">
-        <v>35</v>
+        <v>85</v>
       </c>
       <c r="D79" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E79" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C80">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="D80" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="E80" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B81" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C81">
+        <v>95</v>
+      </c>
+      <c r="D81" t="s">
+        <v>6</v>
+      </c>
+      <c r="E81" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>91</v>
+      </c>
+      <c r="B82" t="s">
+        <v>92</v>
+      </c>
+      <c r="C82">
+        <v>70</v>
+      </c>
+      <c r="D82" t="s">
+        <v>6</v>
+      </c>
+      <c r="E82" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>91</v>
+      </c>
+      <c r="B83" t="s">
+        <v>93</v>
+      </c>
+      <c r="C83">
+        <v>40</v>
+      </c>
+      <c r="D83" t="s">
+        <v>6</v>
+      </c>
+      <c r="E83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" t="s">
+        <v>94</v>
+      </c>
+      <c r="C84">
+        <v>50</v>
+      </c>
+      <c r="D84" t="s">
+        <v>6</v>
+      </c>
+      <c r="E84" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>91</v>
+      </c>
+      <c r="B85" t="s">
+        <v>95</v>
+      </c>
+      <c r="C85">
+        <v>55</v>
+      </c>
+      <c r="D85" t="s">
+        <v>6</v>
+      </c>
+      <c r="E85" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>91</v>
+      </c>
+      <c r="B86" t="s">
+        <v>96</v>
+      </c>
+      <c r="C86">
+        <v>45</v>
+      </c>
+      <c r="D86" t="s">
+        <v>6</v>
+      </c>
+      <c r="E86" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87" t="s">
+        <v>97</v>
+      </c>
+      <c r="C87">
+        <v>50</v>
+      </c>
+      <c r="D87" t="s">
+        <v>6</v>
+      </c>
+      <c r="E87" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>91</v>
+      </c>
+      <c r="B88" t="s">
+        <v>98</v>
+      </c>
+      <c r="C88">
+        <v>55</v>
+      </c>
+      <c r="D88" t="s">
+        <v>6</v>
+      </c>
+      <c r="E88" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>91</v>
+      </c>
+      <c r="B89" t="s">
+        <v>99</v>
+      </c>
+      <c r="C89">
+        <v>80</v>
+      </c>
+      <c r="D89" t="s">
+        <v>6</v>
+      </c>
+      <c r="E89" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>91</v>
+      </c>
+      <c r="B90" t="s">
+        <v>100</v>
+      </c>
+      <c r="C90">
+        <v>35</v>
+      </c>
+      <c r="D90" t="s">
+        <v>6</v>
+      </c>
+      <c r="E90" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>91</v>
+      </c>
+      <c r="B91" t="s">
+        <v>101</v>
+      </c>
+      <c r="C91">
+        <v>150</v>
+      </c>
+      <c r="D91" t="s">
+        <v>6</v>
+      </c>
+      <c r="E91" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>102</v>
+      </c>
+      <c r="B92" t="s">
+        <v>103</v>
+      </c>
+      <c r="C92">
+        <v>80</v>
+      </c>
+      <c r="D92" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" t="s">
+        <v>104</v>
+      </c>
+      <c r="C93">
+        <v>40</v>
+      </c>
+      <c r="D93" t="s">
+        <v>6</v>
+      </c>
+      <c r="E93" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" t="s">
+        <v>105</v>
+      </c>
+      <c r="C94">
+        <v>45</v>
+      </c>
+      <c r="D94" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" t="s">
+        <v>106</v>
+      </c>
+      <c r="C95">
+        <v>50</v>
+      </c>
+      <c r="D95" t="s">
+        <v>6</v>
+      </c>
+      <c r="E95" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>102</v>
+      </c>
+      <c r="B96" t="s">
+        <v>107</v>
+      </c>
+      <c r="C96">
+        <v>30</v>
+      </c>
+      <c r="D96" t="s">
+        <v>6</v>
+      </c>
+      <c r="E96" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>102</v>
+      </c>
+      <c r="B97" t="s">
+        <v>108</v>
+      </c>
+      <c r="C97">
+        <v>30</v>
+      </c>
+      <c r="D97" t="s">
+        <v>6</v>
+      </c>
+      <c r="E97" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>102</v>
+      </c>
+      <c r="B98" t="s">
+        <v>109</v>
+      </c>
+      <c r="C98">
+        <v>25</v>
+      </c>
+      <c r="D98" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>102</v>
+      </c>
+      <c r="B99" t="s">
+        <v>110</v>
+      </c>
+      <c r="C99">
         <v>120</v>
       </c>
-      <c r="D81" t="s">
-        <v>90</v>
-      </c>
-      <c r="E81" t="s">
-        <v>9</v>
+      <c r="D99" t="s">
+        <v>6</v>
+      </c>
+      <c r="E99" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>102</v>
+      </c>
+      <c r="B100" t="s">
+        <v>111</v>
+      </c>
+      <c r="C100">
+        <v>60</v>
+      </c>
+      <c r="D100" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>102</v>
+      </c>
+      <c r="B101" t="s">
+        <v>112</v>
+      </c>
+      <c r="C101">
+        <v>18</v>
+      </c>
+      <c r="D101" t="s">
+        <v>6</v>
+      </c>
+      <c r="E101" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistemas\Pré-Atendimento\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{899DD3AC-58F3-48AE-B405-96445126F0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2354E853-E7BC-4F75-9B7C-2E382CAE3C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
   </bookViews>

--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Sistemas\Pré-Atendimento\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2354E853-E7BC-4F75-9B7C-2E382CAE3C70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA8F1DCA-EEEA-4E59-A6E9-9635E3CEB218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{4158BE41-1E8D-481E-AEE2-F0FC4BF443A8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1205" uniqueCount="313">
   <si>
     <t>nome</t>
   </si>
@@ -48,322 +48,922 @@
     <t>int</t>
   </si>
   <si>
-    <t>Perfumaria</t>
-  </si>
-  <si>
-    <t>Kaiak Masculino 100ml</t>
-  </si>
-  <si>
-    <t>Kaiak Aventura 100ml</t>
-  </si>
-  <si>
-    <t>Essencial Masculino 100ml</t>
-  </si>
-  <si>
-    <t>Essencial Oud 100ml</t>
-  </si>
-  <si>
-    <t>Luna Feminino 75ml</t>
-  </si>
-  <si>
-    <t>Ilía Feminino 75ml</t>
-  </si>
-  <si>
-    <t>Ekos Frescor Maracujá 150ml</t>
-  </si>
-  <si>
-    <t>Ekos Frescor Açaí 150ml</t>
-  </si>
-  <si>
-    <t>Humor Próprio 75ml</t>
-  </si>
-  <si>
-    <t>Humor a Dois 75ml</t>
-  </si>
-  <si>
-    <t>Kriska Feminino 100ml</t>
-  </si>
-  <si>
-    <t>Kriska Drama 100ml</t>
-  </si>
-  <si>
-    <t>Biografia Masculino 100ml</t>
-  </si>
-  <si>
-    <t>Biografia Feminino 100ml</t>
-  </si>
-  <si>
-    <t>Kaiak Urbe 100ml</t>
-  </si>
-  <si>
-    <t>Kaiak Aero 100ml</t>
-  </si>
-  <si>
-    <t>Ilía Secreto 75ml</t>
-  </si>
-  <si>
-    <t>Luna Absoluta 75ml</t>
-  </si>
-  <si>
-    <t>Essencial Exclusivo 100ml</t>
-  </si>
-  <si>
-    <t>Kaiak Oceano 100ml</t>
-  </si>
-  <si>
-    <t>Corpo</t>
-  </si>
-  <si>
-    <t>Hidratante Tododia Ameixa 400ml</t>
-  </si>
-  <si>
-    <t>Hidratante Tododia Macadâmia 400ml</t>
-  </si>
-  <si>
-    <t>Hidratante Tododia Algodão 400ml</t>
-  </si>
-  <si>
-    <t>Hidratante Tododia Manga Rosa 400ml</t>
-  </si>
-  <si>
-    <t>Hidratante Tododia Framboesa 400ml</t>
-  </si>
-  <si>
-    <t>Sabonete Barra Tododia (5un)</t>
-  </si>
-  <si>
-    <t>Sabonete Líquido Tododia 300ml</t>
-  </si>
-  <si>
-    <t>Óleo Corporal Sève Amêndoas 200ml</t>
-  </si>
-  <si>
-    <t>Óleo Corporal Sève Flor de Laranjeira</t>
-  </si>
-  <si>
-    <t>Creme para Mãos Tododia 50ml</t>
-  </si>
-  <si>
-    <t>Desodorante Roll-on Tododia</t>
-  </si>
-  <si>
-    <t>Body Splash Tododia Ameixa</t>
-  </si>
-  <si>
-    <t>Body Splash Tododia Macadâmia</t>
-  </si>
-  <si>
-    <t>Esfoliante Corporal Tododia</t>
-  </si>
-  <si>
-    <t>Hidratante Ekos Castanha 400ml</t>
-  </si>
-  <si>
-    <t>Hidratante Ekos Açaí 400ml</t>
-  </si>
-  <si>
-    <t>Polpa Hidratante Castanha 75g</t>
-  </si>
-  <si>
-    <t>Polpa Hidratante Açaí 75g</t>
-  </si>
-  <si>
-    <t>Sabonete Ekos (3un)</t>
-  </si>
-  <si>
-    <t>Óleo Trifásico Maracujá</t>
-  </si>
-  <si>
-    <t>Creme Firmador Corpo</t>
-  </si>
-  <si>
-    <t>Creme Antiestrias</t>
-  </si>
-  <si>
-    <t>Desodorante Spray</t>
-  </si>
-  <si>
-    <t>Sabonete Líquido Ekos 250ml</t>
-  </si>
-  <si>
-    <t>Kit Hidratante Tododia</t>
-  </si>
-  <si>
-    <t>Cabelos</t>
-  </si>
-  <si>
-    <t>Shampoo Lumina Hidratação 300ml</t>
-  </si>
-  <si>
-    <t>Condicionador Lumina Hidratação 300ml</t>
-  </si>
-  <si>
-    <t>Máscara Lumina 250g</t>
-  </si>
-  <si>
-    <t>Shampoo Lumina Nutrição 300ml</t>
-  </si>
-  <si>
-    <t>Condicionador Lumina Nutrição</t>
-  </si>
-  <si>
-    <t>Shampoo Lumina Reconstrução</t>
-  </si>
-  <si>
-    <t>Condicionador Reconstrução</t>
-  </si>
-  <si>
-    <t>Óleo Capilar Lumina</t>
-  </si>
-  <si>
-    <t>Leave-in Lumina</t>
-  </si>
-  <si>
-    <t>Ampola Capilar Lumina</t>
-  </si>
-  <si>
-    <t>Shampoo Anticaspa</t>
-  </si>
-  <si>
-    <t>Condicionador Anticaspa</t>
-  </si>
-  <si>
-    <t>Máscara Reparadora</t>
-  </si>
-  <si>
-    <t>Creme Pentear Cachos</t>
-  </si>
-  <si>
-    <t>Ativador de Cachos</t>
-  </si>
-  <si>
-    <t>Spray Finalizador</t>
-  </si>
-  <si>
-    <t>Shampoo Infantil</t>
-  </si>
-  <si>
-    <t>Condicionador Infantil</t>
-  </si>
-  <si>
-    <t>Kit Cabelos Lumina</t>
-  </si>
-  <si>
-    <t>Tônico Capilar</t>
-  </si>
-  <si>
-    <t>Rosto</t>
-  </si>
-  <si>
-    <t>Gel Limpeza Chronos</t>
-  </si>
-  <si>
-    <t>Hidratante Chronos</t>
-  </si>
-  <si>
-    <t>Sérum Antissinais</t>
-  </si>
-  <si>
-    <t>Protetor Solar FPS50</t>
-  </si>
-  <si>
-    <t>Protetor FPS30</t>
-  </si>
-  <si>
-    <t>Sabonete Facial</t>
-  </si>
-  <si>
-    <t>Tônico Facial</t>
-  </si>
-  <si>
-    <t>Creme Área Olhos</t>
-  </si>
-  <si>
-    <t>Máscara Facial</t>
-  </si>
-  <si>
-    <t>Esfoliante Facial</t>
-  </si>
-  <si>
-    <t>Água Micelar</t>
-  </si>
-  <si>
-    <t>Kit Rosto Chronos</t>
-  </si>
-  <si>
-    <t>Creme Noturno</t>
-  </si>
-  <si>
-    <t>Creme Diurno</t>
-  </si>
-  <si>
-    <t>Sérum Vitamina C</t>
-  </si>
-  <si>
-    <t>Maquiagem</t>
-  </si>
-  <si>
-    <t>Base Una</t>
-  </si>
-  <si>
-    <t>Batom Matte</t>
-  </si>
-  <si>
-    <t>Máscara Cílios</t>
-  </si>
-  <si>
-    <t>Pó Compacto</t>
-  </si>
-  <si>
-    <t>Corretivo</t>
-  </si>
-  <si>
-    <t>Blush</t>
-  </si>
-  <si>
-    <t>Iluminador</t>
-  </si>
-  <si>
-    <t>Paleta Sombras</t>
-  </si>
-  <si>
-    <t>Delineador</t>
-  </si>
-  <si>
-    <t>Kit Maquiagem</t>
-  </si>
-  <si>
-    <t>Infantil</t>
-  </si>
-  <si>
-    <t>Colônia Mamãe e Bebê</t>
-  </si>
-  <si>
-    <t>Sabonete Líquido Bebê</t>
-  </si>
-  <si>
-    <t>Hidratante Bebê</t>
-  </si>
-  <si>
-    <t>Óleo Bebê</t>
-  </si>
-  <si>
-    <t>Shampoo Bebê</t>
-  </si>
-  <si>
-    <t>Condicionador Bebê</t>
-  </si>
-  <si>
-    <t>Lenço Umedecido</t>
-  </si>
-  <si>
-    <t>Kit Bebê Completo</t>
-  </si>
-  <si>
-    <t>Colônia Infantil</t>
-  </si>
-  <si>
-    <t>Sabonete Barra Bebê</t>
+    <t>Iluminação</t>
+  </si>
+  <si>
+    <t>Refletor LED 1</t>
+  </si>
+  <si>
+    <t>Refletor LED 2</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 3</t>
+  </si>
+  <si>
+    <t>Luminária 4</t>
+  </si>
+  <si>
+    <t>Refletor LED 5</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 6</t>
+  </si>
+  <si>
+    <t>Refletor LED 7</t>
+  </si>
+  <si>
+    <t>Fita LED 8</t>
+  </si>
+  <si>
+    <t>Luminária 9</t>
+  </si>
+  <si>
+    <t>Refletor LED 10</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 11</t>
+  </si>
+  <si>
+    <t>Luminária 12</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 13</t>
+  </si>
+  <si>
+    <t>Refletor LED 14</t>
+  </si>
+  <si>
+    <t>Refletor LED 15</t>
+  </si>
+  <si>
+    <t>Refletor LED 16</t>
+  </si>
+  <si>
+    <t>Refletor LED 17</t>
+  </si>
+  <si>
+    <t>Luminária 18</t>
+  </si>
+  <si>
+    <t>Luminária 19</t>
+  </si>
+  <si>
+    <t>Fita LED 20</t>
+  </si>
+  <si>
+    <t>Luminária 21</t>
+  </si>
+  <si>
+    <t>Refletor LED 22</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 23</t>
+  </si>
+  <si>
+    <t>Fita LED 24</t>
+  </si>
+  <si>
+    <t>Refletor LED 25</t>
+  </si>
+  <si>
+    <t>Fita LED 26</t>
+  </si>
+  <si>
+    <t>Fita LED 27</t>
+  </si>
+  <si>
+    <t>Luminária 28</t>
+  </si>
+  <si>
+    <t>Luminária 29</t>
+  </si>
+  <si>
+    <t>Refletor LED 30</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 31</t>
+  </si>
+  <si>
+    <t>Refletor LED 32</t>
+  </si>
+  <si>
+    <t>Refletor LED 33</t>
+  </si>
+  <si>
+    <t>Luminária 34</t>
+  </si>
+  <si>
+    <t>Fita LED 35</t>
+  </si>
+  <si>
+    <t>Fita LED 36</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 37</t>
+  </si>
+  <si>
+    <t>Luminária 38</t>
+  </si>
+  <si>
+    <t>Refletor LED 39</t>
+  </si>
+  <si>
+    <t>Fita LED 40</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 41</t>
+  </si>
+  <si>
+    <t>Fita LED 42</t>
+  </si>
+  <si>
+    <t>Luminária 43</t>
+  </si>
+  <si>
+    <t>Refletor LED 44</t>
+  </si>
+  <si>
+    <t>Luminária 45</t>
+  </si>
+  <si>
+    <t>Fita LED 46</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 47</t>
+  </si>
+  <si>
+    <t>Luminária 48</t>
+  </si>
+  <si>
+    <t>Refletor LED 49</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 50</t>
+  </si>
+  <si>
+    <t>Luminária 51</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 52</t>
+  </si>
+  <si>
+    <t>Refletor LED 53</t>
+  </si>
+  <si>
+    <t>Refletor LED 54</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 55</t>
+  </si>
+  <si>
+    <t>Refletor LED 56</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 57</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 58</t>
+  </si>
+  <si>
+    <t>Refletor LED 59</t>
+  </si>
+  <si>
+    <t>Fita LED 60</t>
+  </si>
+  <si>
+    <t>Refletor LED 61</t>
+  </si>
+  <si>
+    <t>Luminária 62</t>
+  </si>
+  <si>
+    <t>Fita LED 63</t>
+  </si>
+  <si>
+    <t>Luminária 64</t>
+  </si>
+  <si>
+    <t>Fita LED 65</t>
+  </si>
+  <si>
+    <t>Refletor LED 66</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 67</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 68</t>
+  </si>
+  <si>
+    <t>Fita LED 69</t>
+  </si>
+  <si>
+    <t>Fita LED 70</t>
+  </si>
+  <si>
+    <t>Refletor LED 71</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 72</t>
+  </si>
+  <si>
+    <t>Fita LED 73</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 74</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 75</t>
+  </si>
+  <si>
+    <t>Fita LED 76</t>
+  </si>
+  <si>
+    <t>Luminária 77</t>
+  </si>
+  <si>
+    <t>Luminária 78</t>
+  </si>
+  <si>
+    <t>Luminária 79</t>
+  </si>
+  <si>
+    <t>Refletor LED 80</t>
+  </si>
+  <si>
+    <t>Luminária 81</t>
+  </si>
+  <si>
+    <t>Fita LED 82</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 83</t>
+  </si>
+  <si>
+    <t>Fita LED 84</t>
+  </si>
+  <si>
+    <t>Refletor LED 85</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 86</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 87</t>
+  </si>
+  <si>
+    <t>Fita LED 88</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 89</t>
+  </si>
+  <si>
+    <t>Refletor LED 90</t>
+  </si>
+  <si>
+    <t>Fita LED 91</t>
+  </si>
+  <si>
+    <t>Luminária 92</t>
+  </si>
+  <si>
+    <t>Fita LED 93</t>
+  </si>
+  <si>
+    <t>Luminária 94</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 95</t>
+  </si>
+  <si>
+    <t>Lâmpada LED 96</t>
+  </si>
+  <si>
+    <t>Luminária 97</t>
+  </si>
+  <si>
+    <t>Luminária 98</t>
+  </si>
+  <si>
+    <t>Fita LED 99</t>
+  </si>
+  <si>
+    <t>Tomadas e Interruptores</t>
+  </si>
+  <si>
+    <t>Tomada 1</t>
+  </si>
+  <si>
+    <t>Conjunto 2</t>
+  </si>
+  <si>
+    <t>Espelho 3</t>
+  </si>
+  <si>
+    <t>Conjunto 4</t>
+  </si>
+  <si>
+    <t>Tomada 5</t>
+  </si>
+  <si>
+    <t>Tomada 6</t>
+  </si>
+  <si>
+    <t>Conjunto 7</t>
+  </si>
+  <si>
+    <t>Conjunto 8</t>
+  </si>
+  <si>
+    <t>Espelho 9</t>
+  </si>
+  <si>
+    <t>Conjunto 10</t>
+  </si>
+  <si>
+    <t>Interruptor 11</t>
+  </si>
+  <si>
+    <t>Espelho 12</t>
+  </si>
+  <si>
+    <t>Conjunto 13</t>
+  </si>
+  <si>
+    <t>Conjunto 14</t>
+  </si>
+  <si>
+    <t>Espelho 15</t>
+  </si>
+  <si>
+    <t>Tomada 16</t>
+  </si>
+  <si>
+    <t>Tomada 17</t>
+  </si>
+  <si>
+    <t>Conjunto 18</t>
+  </si>
+  <si>
+    <t>Conjunto 19</t>
+  </si>
+  <si>
+    <t>Conjunto 20</t>
+  </si>
+  <si>
+    <t>Interruptor 21</t>
+  </si>
+  <si>
+    <t>Interruptor 22</t>
+  </si>
+  <si>
+    <t>Espelho 23</t>
+  </si>
+  <si>
+    <t>Espelho 24</t>
+  </si>
+  <si>
+    <t>Conjunto 25</t>
+  </si>
+  <si>
+    <t>Interruptor 26</t>
+  </si>
+  <si>
+    <t>Tomada 27</t>
+  </si>
+  <si>
+    <t>Tomada 28</t>
+  </si>
+  <si>
+    <t>Conjunto 29</t>
+  </si>
+  <si>
+    <t>Conjunto 30</t>
+  </si>
+  <si>
+    <t>Conjunto 31</t>
+  </si>
+  <si>
+    <t>Tomada 32</t>
+  </si>
+  <si>
+    <t>Interruptor 33</t>
+  </si>
+  <si>
+    <t>Espelho 34</t>
+  </si>
+  <si>
+    <t>Conjunto 35</t>
+  </si>
+  <si>
+    <t>Interruptor 36</t>
+  </si>
+  <si>
+    <t>Conjunto 37</t>
+  </si>
+  <si>
+    <t>Tomada 38</t>
+  </si>
+  <si>
+    <t>Tomada 39</t>
+  </si>
+  <si>
+    <t>Tomada 40</t>
+  </si>
+  <si>
+    <t>Conjunto 41</t>
+  </si>
+  <si>
+    <t>Tomada 42</t>
+  </si>
+  <si>
+    <t>Interruptor 43</t>
+  </si>
+  <si>
+    <t>Conjunto 44</t>
+  </si>
+  <si>
+    <t>Conjunto 45</t>
+  </si>
+  <si>
+    <t>Interruptor 46</t>
+  </si>
+  <si>
+    <t>Tomada 47</t>
+  </si>
+  <si>
+    <t>Espelho 48</t>
+  </si>
+  <si>
+    <t>Conjunto 49</t>
+  </si>
+  <si>
+    <t>Espelho 50</t>
+  </si>
+  <si>
+    <t>Espelho 51</t>
+  </si>
+  <si>
+    <t>Espelho 52</t>
+  </si>
+  <si>
+    <t>Conjunto 53</t>
+  </si>
+  <si>
+    <t>Espelho 54</t>
+  </si>
+  <si>
+    <t>Espelho 55</t>
+  </si>
+  <si>
+    <t>Tomada 56</t>
+  </si>
+  <si>
+    <t>Conjunto 57</t>
+  </si>
+  <si>
+    <t>Tomada 58</t>
+  </si>
+  <si>
+    <t>Tomada 59</t>
+  </si>
+  <si>
+    <t>Conjunto 60</t>
+  </si>
+  <si>
+    <t>Interruptor 61</t>
+  </si>
+  <si>
+    <t>Interruptor 62</t>
+  </si>
+  <si>
+    <t>Conjunto 63</t>
+  </si>
+  <si>
+    <t>Interruptor 64</t>
+  </si>
+  <si>
+    <t>Espelho 65</t>
+  </si>
+  <si>
+    <t>Interruptor 66</t>
+  </si>
+  <si>
+    <t>Espelho 67</t>
+  </si>
+  <si>
+    <t>Espelho 68</t>
+  </si>
+  <si>
+    <t>Interruptor 69</t>
+  </si>
+  <si>
+    <t>Espelho 70</t>
+  </si>
+  <si>
+    <t>Interruptor 71</t>
+  </si>
+  <si>
+    <t>Conjunto 72</t>
+  </si>
+  <si>
+    <t>Espelho 73</t>
+  </si>
+  <si>
+    <t>Tomada 74</t>
+  </si>
+  <si>
+    <t>Conjunto 75</t>
+  </si>
+  <si>
+    <t>Interruptor 76</t>
+  </si>
+  <si>
+    <t>Espelho 77</t>
+  </si>
+  <si>
+    <t>Interruptor 78</t>
+  </si>
+  <si>
+    <t>Interruptor 79</t>
+  </si>
+  <si>
+    <t>Tomada 80</t>
+  </si>
+  <si>
+    <t>Interruptor 81</t>
+  </si>
+  <si>
+    <t>Conjunto 82</t>
+  </si>
+  <si>
+    <t>Espelho 83</t>
+  </si>
+  <si>
+    <t>Interruptor 84</t>
+  </si>
+  <si>
+    <t>Conjunto 85</t>
+  </si>
+  <si>
+    <t>Tomada 86</t>
+  </si>
+  <si>
+    <t>Conjunto 87</t>
+  </si>
+  <si>
+    <t>Tomada 88</t>
+  </si>
+  <si>
+    <t>Interruptor 89</t>
+  </si>
+  <si>
+    <t>Interruptor 90</t>
+  </si>
+  <si>
+    <t>Espelho 91</t>
+  </si>
+  <si>
+    <t>Interruptor 92</t>
+  </si>
+  <si>
+    <t>Tomada 93</t>
+  </si>
+  <si>
+    <t>Conjunto 94</t>
+  </si>
+  <si>
+    <t>Interruptor 95</t>
+  </si>
+  <si>
+    <t>Conjunto 96</t>
+  </si>
+  <si>
+    <t>Tomada 97</t>
+  </si>
+  <si>
+    <t>Tomada 98</t>
+  </si>
+  <si>
+    <t>Espelho 99</t>
+  </si>
+  <si>
+    <t>Fios e Cabos</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 1</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>Fio Flexível 2</t>
+  </si>
+  <si>
+    <t>Cabo PP 3</t>
+  </si>
+  <si>
+    <t>Fio Flexível 4</t>
+  </si>
+  <si>
+    <t>Fio Flexível 5</t>
+  </si>
+  <si>
+    <t>Fio Flexível 6</t>
+  </si>
+  <si>
+    <t>Fio Flexível 7</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 8</t>
+  </si>
+  <si>
+    <t>Cabo PP 9</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 10</t>
+  </si>
+  <si>
+    <t>Cabo PP 11</t>
+  </si>
+  <si>
+    <t>Fio Flexível 12</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 13</t>
+  </si>
+  <si>
+    <t>Fio Flexível 14</t>
+  </si>
+  <si>
+    <t>Fio Flexível 15</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 16</t>
+  </si>
+  <si>
+    <t>Fio Flexível 17</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 18</t>
+  </si>
+  <si>
+    <t>Cabo PP 19</t>
+  </si>
+  <si>
+    <t>Fio Flexível 20</t>
+  </si>
+  <si>
+    <t>Cabo PP 21</t>
+  </si>
+  <si>
+    <t>Fio Flexível 22</t>
+  </si>
+  <si>
+    <t>Fio Flexível 23</t>
+  </si>
+  <si>
+    <t>Cabo PP 24</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 25</t>
+  </si>
+  <si>
+    <t>Fio Flexível 26</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 27</t>
+  </si>
+  <si>
+    <t>Cabo PP 28</t>
+  </si>
+  <si>
+    <t>Fio Flexível 29</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 30</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 31</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 32</t>
+  </si>
+  <si>
+    <t>Cabo PP 33</t>
+  </si>
+  <si>
+    <t>Fio Flexível 34</t>
+  </si>
+  <si>
+    <t>Cabo PP 35</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 36</t>
+  </si>
+  <si>
+    <t>Fio Flexível 37</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 38</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 39</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 40</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 41</t>
+  </si>
+  <si>
+    <t>Fio Flexível 42</t>
+  </si>
+  <si>
+    <t>Cabo PP 43</t>
+  </si>
+  <si>
+    <t>Fio Flexível 44</t>
+  </si>
+  <si>
+    <t>Fio Flexível 45</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 46</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 47</t>
+  </si>
+  <si>
+    <t>Fio Flexível 48</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 49</t>
+  </si>
+  <si>
+    <t>Fio Flexível 50</t>
+  </si>
+  <si>
+    <t>Cabo PP 51</t>
+  </si>
+  <si>
+    <t>Fio Flexível 52</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 53</t>
+  </si>
+  <si>
+    <t>Fio Flexível 54</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 55</t>
+  </si>
+  <si>
+    <t>Fio Flexível 56</t>
+  </si>
+  <si>
+    <t>Cabo PP 57</t>
+  </si>
+  <si>
+    <t>Fio Flexível 58</t>
+  </si>
+  <si>
+    <t>Cabo PP 59</t>
+  </si>
+  <si>
+    <t>Fio Flexível 60</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 61</t>
+  </si>
+  <si>
+    <t>Cabo PP 62</t>
+  </si>
+  <si>
+    <t>Fio Flexível 63</t>
+  </si>
+  <si>
+    <t>Fio Flexível 64</t>
+  </si>
+  <si>
+    <t>Cabo PP 65</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 66</t>
+  </si>
+  <si>
+    <t>Cabo PP 67</t>
+  </si>
+  <si>
+    <t>Fio Flexível 68</t>
+  </si>
+  <si>
+    <t>Cabo PP 69</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 70</t>
+  </si>
+  <si>
+    <t>Fio Flexível 71</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 72</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 73</t>
+  </si>
+  <si>
+    <t>Fio Flexível 74</t>
+  </si>
+  <si>
+    <t>Cabo PP 75</t>
+  </si>
+  <si>
+    <t>Cabo PP 76</t>
+  </si>
+  <si>
+    <t>Fio Flexível 77</t>
+  </si>
+  <si>
+    <t>Cabo PP 78</t>
+  </si>
+  <si>
+    <t>Cabo PP 79</t>
+  </si>
+  <si>
+    <t>Fio Flexível 80</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 81</t>
+  </si>
+  <si>
+    <t>Cabo PP 82</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 83</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 84</t>
+  </si>
+  <si>
+    <t>Fio Flexível 85</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 86</t>
+  </si>
+  <si>
+    <t>Cabo PP 87</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 88</t>
+  </si>
+  <si>
+    <t>Fio Flexível 89</t>
+  </si>
+  <si>
+    <t>Cabo PP 90</t>
+  </si>
+  <si>
+    <t>Cabo PP 91</t>
+  </si>
+  <si>
+    <t>Cabo PP 92</t>
+  </si>
+  <si>
+    <t>Fio Flexível 93</t>
+  </si>
+  <si>
+    <t>Fio Flexível 94</t>
+  </si>
+  <si>
+    <t>Cabo PP 95</t>
+  </si>
+  <si>
+    <t>Cabo PP 96</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 97</t>
+  </si>
+  <si>
+    <t>Cabo Rígido 98</t>
+  </si>
+  <si>
+    <t>Cabo PP 99</t>
+  </si>
+  <si>
+    <t>Disjuntores</t>
+  </si>
+  <si>
+    <t>DR 1</t>
+  </si>
+  <si>
+    <t>DR 2</t>
+  </si>
+  <si>
+    <t>DR 3</t>
   </si>
 </sst>
 </file>
@@ -715,7 +1315,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22BA13D2-8BD4-4A6A-90F8-DD922486DCB7}">
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E301"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -748,7 +1348,7 @@
         <v>8</v>
       </c>
       <c r="C2">
-        <v>130</v>
+        <v>279</v>
       </c>
       <c r="D2" t="s">
         <v>6</v>
@@ -765,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>135</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
         <v>6</v>
@@ -782,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="C4">
-        <v>160</v>
+        <v>136</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -799,7 +1399,7 @@
         <v>11</v>
       </c>
       <c r="C5">
-        <v>180</v>
+        <v>237</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -816,7 +1416,7 @@
         <v>12</v>
       </c>
       <c r="C6">
-        <v>140</v>
+        <v>221</v>
       </c>
       <c r="D6" t="s">
         <v>6</v>
@@ -833,7 +1433,7 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
         <v>6</v>
@@ -850,7 +1450,7 @@
         <v>14</v>
       </c>
       <c r="C8">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D8" t="s">
         <v>6</v>
@@ -867,7 +1467,7 @@
         <v>15</v>
       </c>
       <c r="C9">
-        <v>120</v>
+        <v>198</v>
       </c>
       <c r="D9" t="s">
         <v>6</v>
@@ -884,7 +1484,7 @@
         <v>16</v>
       </c>
       <c r="C10">
-        <v>110</v>
+        <v>265</v>
       </c>
       <c r="D10" t="s">
         <v>6</v>
@@ -901,7 +1501,7 @@
         <v>17</v>
       </c>
       <c r="C11">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="D11" t="s">
         <v>6</v>
@@ -918,7 +1518,7 @@
         <v>18</v>
       </c>
       <c r="C12">
-        <v>95</v>
+        <v>224</v>
       </c>
       <c r="D12" t="s">
         <v>6</v>
@@ -935,7 +1535,7 @@
         <v>19</v>
       </c>
       <c r="C13">
-        <v>100</v>
+        <v>257</v>
       </c>
       <c r="D13" t="s">
         <v>6</v>
@@ -952,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="C14">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="D14" t="s">
         <v>6</v>
@@ -969,7 +1569,7 @@
         <v>21</v>
       </c>
       <c r="C15">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
         <v>6</v>
@@ -986,7 +1586,7 @@
         <v>22</v>
       </c>
       <c r="C16">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D16" t="s">
         <v>6</v>
@@ -1003,7 +1603,7 @@
         <v>23</v>
       </c>
       <c r="C17">
-        <v>145</v>
+        <v>101</v>
       </c>
       <c r="D17" t="s">
         <v>6</v>
@@ -1020,7 +1620,7 @@
         <v>24</v>
       </c>
       <c r="C18">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="D18" t="s">
         <v>6</v>
@@ -1037,7 +1637,7 @@
         <v>25</v>
       </c>
       <c r="C19">
-        <v>150</v>
+        <v>192</v>
       </c>
       <c r="D19" t="s">
         <v>6</v>
@@ -1054,7 +1654,7 @@
         <v>26</v>
       </c>
       <c r="C20">
-        <v>190</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>6</v>
@@ -1071,7 +1671,7 @@
         <v>27</v>
       </c>
       <c r="C21">
-        <v>150</v>
+        <v>52</v>
       </c>
       <c r="D21" t="s">
         <v>6</v>
@@ -1082,13 +1682,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>7</v>
+      </c>
+      <c r="B22" t="s">
         <v>28</v>
       </c>
-      <c r="B22" t="s">
-        <v>29</v>
-      </c>
       <c r="C22">
-        <v>40</v>
+        <v>239</v>
       </c>
       <c r="D22" t="s">
         <v>6</v>
@@ -1099,13 +1699,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C23">
-        <v>40</v>
+        <v>277</v>
       </c>
       <c r="D23" t="s">
         <v>6</v>
@@ -1116,13 +1716,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C24">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="D24" t="s">
         <v>6</v>
@@ -1133,13 +1733,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C25">
-        <v>40</v>
+        <v>135</v>
       </c>
       <c r="D25" t="s">
         <v>6</v>
@@ -1150,13 +1750,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C26">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="D26" t="s">
         <v>6</v>
@@ -1167,13 +1767,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C27">
-        <v>20</v>
+        <v>218</v>
       </c>
       <c r="D27" t="s">
         <v>6</v>
@@ -1184,13 +1784,13 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C28">
-        <v>25</v>
+        <v>128</v>
       </c>
       <c r="D28" t="s">
         <v>6</v>
@@ -1201,13 +1801,13 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C29">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="D29" t="s">
         <v>6</v>
@@ -1218,13 +1818,13 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C30">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
         <v>6</v>
@@ -1235,13 +1835,13 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C31">
-        <v>18</v>
+        <v>296</v>
       </c>
       <c r="D31" t="s">
         <v>6</v>
@@ -1252,13 +1852,13 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C32">
-        <v>12</v>
+        <v>69</v>
       </c>
       <c r="D32" t="s">
         <v>6</v>
@@ -1269,13 +1869,13 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B33" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C33">
-        <v>45</v>
+        <v>87</v>
       </c>
       <c r="D33" t="s">
         <v>6</v>
@@ -1286,13 +1886,13 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C34">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="D34" t="s">
         <v>6</v>
@@ -1303,13 +1903,13 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B35" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C35">
-        <v>35</v>
+        <v>168</v>
       </c>
       <c r="D35" t="s">
         <v>6</v>
@@ -1320,13 +1920,13 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B36" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C36">
-        <v>55</v>
+        <v>90</v>
       </c>
       <c r="D36" t="s">
         <v>6</v>
@@ -1337,13 +1937,13 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B37" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C37">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D37" t="s">
         <v>6</v>
@@ -1354,13 +1954,13 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C38">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="D38" t="s">
         <v>6</v>
@@ -1371,13 +1971,13 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39">
-        <v>30</v>
+        <v>208</v>
       </c>
       <c r="D39" t="s">
         <v>6</v>
@@ -1388,13 +1988,13 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40">
-        <v>18</v>
+        <v>236</v>
       </c>
       <c r="D40" t="s">
         <v>6</v>
@@ -1405,13 +2005,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C41">
-        <v>75</v>
+        <v>121</v>
       </c>
       <c r="D41" t="s">
         <v>6</v>
@@ -1422,13 +2022,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B42" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C42">
-        <v>80</v>
+        <v>169</v>
       </c>
       <c r="D42" t="s">
         <v>6</v>
@@ -1439,13 +2039,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C43">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D43" t="s">
         <v>6</v>
@@ -1456,13 +2056,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C44">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="D44" t="s">
         <v>6</v>
@@ -1473,13 +2073,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B45" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C45">
-        <v>28</v>
+        <v>294</v>
       </c>
       <c r="D45" t="s">
         <v>6</v>
@@ -1490,13 +2090,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C46">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
         <v>6</v>
@@ -1507,13 +2107,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B47" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C47">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="D47" t="s">
         <v>6</v>
@@ -1524,13 +2124,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
         <v>54</v>
       </c>
-      <c r="B48" t="s">
-        <v>56</v>
-      </c>
       <c r="C48">
-        <v>32</v>
+        <v>236</v>
       </c>
       <c r="D48" t="s">
         <v>6</v>
@@ -1541,13 +2141,13 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>7</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49">
         <v>54</v>
-      </c>
-      <c r="B49" t="s">
-        <v>57</v>
-      </c>
-      <c r="C49">
-        <v>50</v>
       </c>
       <c r="D49" t="s">
         <v>6</v>
@@ -1558,13 +2158,13 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B50" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C50">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="D50" t="s">
         <v>6</v>
@@ -1575,13 +2175,13 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B51" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C51">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="D51" t="s">
         <v>6</v>
@@ -1592,13 +2192,13 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B52" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C52">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D52" t="s">
         <v>6</v>
@@ -1609,13 +2209,13 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B53" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C53">
-        <v>34</v>
+        <v>273</v>
       </c>
       <c r="D53" t="s">
         <v>6</v>
@@ -1626,13 +2226,13 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B54" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C54">
-        <v>45</v>
+        <v>266</v>
       </c>
       <c r="D54" t="s">
         <v>6</v>
@@ -1643,13 +2243,13 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C55">
-        <v>40</v>
+        <v>202</v>
       </c>
       <c r="D55" t="s">
         <v>6</v>
@@ -1660,13 +2260,13 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C56">
-        <v>15</v>
+        <v>165</v>
       </c>
       <c r="D56" t="s">
         <v>6</v>
@@ -1677,13 +2277,13 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C57">
-        <v>28</v>
+        <v>203</v>
       </c>
       <c r="D57" t="s">
         <v>6</v>
@@ -1694,13 +2294,13 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B58" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C58">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D58" t="s">
         <v>6</v>
@@ -1711,13 +2311,13 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B59" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C59">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="D59" t="s">
         <v>6</v>
@@ -1728,13 +2328,13 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B60" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C60">
-        <v>35</v>
+        <v>155</v>
       </c>
       <c r="D60" t="s">
         <v>6</v>
@@ -1745,13 +2345,13 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B61" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C61">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D61" t="s">
         <v>6</v>
@@ -1762,13 +2362,13 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C62">
-        <v>30</v>
+        <v>254</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
@@ -1779,13 +2379,13 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B63" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C63">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
         <v>6</v>
@@ -1796,13 +2396,13 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B64" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C64">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="D64" t="s">
         <v>6</v>
@@ -1813,13 +2413,13 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C65">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="D65" t="s">
         <v>6</v>
@@ -1830,13 +2430,13 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>54</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C66">
-        <v>42</v>
+        <v>82</v>
       </c>
       <c r="D66" t="s">
         <v>6</v>
@@ -1847,13 +2447,13 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B67" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C67">
-        <v>46</v>
+        <v>115</v>
       </c>
       <c r="D67" t="s">
         <v>6</v>
@@ -1864,13 +2464,13 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B68" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C68">
-        <v>80</v>
+        <v>240</v>
       </c>
       <c r="D68" t="s">
         <v>6</v>
@@ -1881,13 +2481,13 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>7</v>
+      </c>
+      <c r="B69" t="s">
         <v>75</v>
       </c>
-      <c r="B69" t="s">
-        <v>78</v>
-      </c>
       <c r="C69">
-        <v>120</v>
+        <v>242</v>
       </c>
       <c r="D69" t="s">
         <v>6</v>
@@ -1898,13 +2498,13 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B70" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C70">
-        <v>60</v>
+        <v>144</v>
       </c>
       <c r="D70" t="s">
         <v>6</v>
@@ -1915,13 +2515,13 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B71" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C71">
-        <v>50</v>
+        <v>177</v>
       </c>
       <c r="D71" t="s">
         <v>6</v>
@@ -1932,13 +2532,13 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B72" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C72">
-        <v>30</v>
+        <v>201</v>
       </c>
       <c r="D72" t="s">
         <v>6</v>
@@ -1949,13 +2549,13 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B73" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C73">
-        <v>35</v>
+        <v>158</v>
       </c>
       <c r="D73" t="s">
         <v>6</v>
@@ -1966,13 +2566,13 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B74" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C74">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="D74" t="s">
         <v>6</v>
@@ -1983,13 +2583,13 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B75" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C75">
-        <v>45</v>
+        <v>152</v>
       </c>
       <c r="D75" t="s">
         <v>6</v>
@@ -2000,13 +2600,13 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B76" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C76">
-        <v>38</v>
+        <v>254</v>
       </c>
       <c r="D76" t="s">
         <v>6</v>
@@ -2017,13 +2617,13 @@
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B77" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C77">
-        <v>42</v>
+        <v>237</v>
       </c>
       <c r="D77" t="s">
         <v>6</v>
@@ -2034,13 +2634,13 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B78" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C78">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="D78" t="s">
         <v>6</v>
@@ -2051,13 +2651,13 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B79" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C79">
-        <v>85</v>
+        <v>7</v>
       </c>
       <c r="D79" t="s">
         <v>6</v>
@@ -2068,13 +2668,13 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C80">
-        <v>85</v>
+        <v>208</v>
       </c>
       <c r="D80" t="s">
         <v>6</v>
@@ -2085,13 +2685,13 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>75</v>
+        <v>7</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C81">
-        <v>95</v>
+        <v>289</v>
       </c>
       <c r="D81" t="s">
         <v>6</v>
@@ -2102,13 +2702,13 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C82">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="D82" t="s">
         <v>6</v>
@@ -2119,13 +2719,13 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C83">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="D83" t="s">
         <v>6</v>
@@ -2136,13 +2736,13 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B84" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C84">
-        <v>50</v>
+        <v>219</v>
       </c>
       <c r="D84" t="s">
         <v>6</v>
@@ -2153,13 +2753,13 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85" t="s">
         <v>91</v>
       </c>
-      <c r="B85" t="s">
-        <v>95</v>
-      </c>
       <c r="C85">
-        <v>55</v>
+        <v>132</v>
       </c>
       <c r="D85" t="s">
         <v>6</v>
@@ -2170,13 +2770,13 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B86" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C86">
-        <v>45</v>
+        <v>300</v>
       </c>
       <c r="D86" t="s">
         <v>6</v>
@@ -2187,13 +2787,13 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B87" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C87">
-        <v>50</v>
+        <v>153</v>
       </c>
       <c r="D87" t="s">
         <v>6</v>
@@ -2204,13 +2804,13 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B88" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C88">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="D88" t="s">
         <v>6</v>
@@ -2221,13 +2821,13 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B89" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="C89">
-        <v>80</v>
+        <v>251</v>
       </c>
       <c r="D89" t="s">
         <v>6</v>
@@ -2238,13 +2838,13 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B90" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C90">
-        <v>35</v>
+        <v>187</v>
       </c>
       <c r="D90" t="s">
         <v>6</v>
@@ -2255,13 +2855,13 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>7</v>
       </c>
       <c r="B91" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C91">
-        <v>150</v>
+        <v>196</v>
       </c>
       <c r="D91" t="s">
         <v>6</v>
@@ -2272,13 +2872,13 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B92" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C92">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D92" t="s">
         <v>6</v>
@@ -2289,13 +2889,13 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B93" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C93">
-        <v>40</v>
+        <v>178</v>
       </c>
       <c r="D93" t="s">
         <v>6</v>
@@ -2306,13 +2906,13 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B94" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C94">
-        <v>45</v>
+        <v>293</v>
       </c>
       <c r="D94" t="s">
         <v>6</v>
@@ -2323,13 +2923,13 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B95" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C95">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="D95" t="s">
         <v>6</v>
@@ -2340,13 +2940,13 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
+        <v>7</v>
+      </c>
+      <c r="B96" t="s">
         <v>102</v>
       </c>
-      <c r="B96" t="s">
-        <v>107</v>
-      </c>
       <c r="C96">
-        <v>30</v>
+        <v>66</v>
       </c>
       <c r="D96" t="s">
         <v>6</v>
@@ -2357,13 +2957,13 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B97" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C97">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D97" t="s">
         <v>6</v>
@@ -2374,13 +2974,13 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B98" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C98">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D98" t="s">
         <v>6</v>
@@ -2391,13 +2991,13 @@
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B99" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C99">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="D99" t="s">
         <v>6</v>
@@ -2408,13 +3008,13 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B100" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C100">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D100" t="s">
         <v>6</v>
@@ -2425,18 +3025,3418 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B101" t="s">
+        <v>108</v>
+      </c>
+      <c r="C101">
+        <v>67</v>
+      </c>
+      <c r="D101" t="s">
+        <v>6</v>
+      </c>
+      <c r="E101" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>107</v>
+      </c>
+      <c r="B102" t="s">
+        <v>109</v>
+      </c>
+      <c r="C102">
+        <v>268</v>
+      </c>
+      <c r="D102" t="s">
+        <v>6</v>
+      </c>
+      <c r="E102" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103" t="s">
+        <v>110</v>
+      </c>
+      <c r="C103">
+        <v>281</v>
+      </c>
+      <c r="D103" t="s">
+        <v>6</v>
+      </c>
+      <c r="E103" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>107</v>
+      </c>
+      <c r="B104" t="s">
+        <v>111</v>
+      </c>
+      <c r="C104">
+        <v>165</v>
+      </c>
+      <c r="D104" t="s">
+        <v>6</v>
+      </c>
+      <c r="E104" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>107</v>
+      </c>
+      <c r="B105" t="s">
         <v>112</v>
       </c>
-      <c r="C101">
-        <v>18</v>
-      </c>
-      <c r="D101" t="s">
-        <v>6</v>
-      </c>
-      <c r="E101" t="s">
+      <c r="C105">
+        <v>268</v>
+      </c>
+      <c r="D105" t="s">
+        <v>6</v>
+      </c>
+      <c r="E105" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>107</v>
+      </c>
+      <c r="B106" t="s">
+        <v>113</v>
+      </c>
+      <c r="C106">
+        <v>239</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+      <c r="E106" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>107</v>
+      </c>
+      <c r="B107" t="s">
+        <v>114</v>
+      </c>
+      <c r="C107">
+        <v>168</v>
+      </c>
+      <c r="D107" t="s">
+        <v>6</v>
+      </c>
+      <c r="E107" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>107</v>
+      </c>
+      <c r="B108" t="s">
+        <v>115</v>
+      </c>
+      <c r="C108">
+        <v>53</v>
+      </c>
+      <c r="D108" t="s">
+        <v>6</v>
+      </c>
+      <c r="E108" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>107</v>
+      </c>
+      <c r="B109" t="s">
+        <v>116</v>
+      </c>
+      <c r="C109">
+        <v>127</v>
+      </c>
+      <c r="D109" t="s">
+        <v>6</v>
+      </c>
+      <c r="E109" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>107</v>
+      </c>
+      <c r="B110" t="s">
+        <v>117</v>
+      </c>
+      <c r="C110">
+        <v>269</v>
+      </c>
+      <c r="D110" t="s">
+        <v>6</v>
+      </c>
+      <c r="E110" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>107</v>
+      </c>
+      <c r="B111" t="s">
+        <v>118</v>
+      </c>
+      <c r="C111">
+        <v>181</v>
+      </c>
+      <c r="D111" t="s">
+        <v>6</v>
+      </c>
+      <c r="E111" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>107</v>
+      </c>
+      <c r="B112" t="s">
+        <v>119</v>
+      </c>
+      <c r="C112">
+        <v>44</v>
+      </c>
+      <c r="D112" t="s">
+        <v>6</v>
+      </c>
+      <c r="E112" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>107</v>
+      </c>
+      <c r="B113" t="s">
+        <v>120</v>
+      </c>
+      <c r="C113">
+        <v>155</v>
+      </c>
+      <c r="D113" t="s">
+        <v>6</v>
+      </c>
+      <c r="E113" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>107</v>
+      </c>
+      <c r="B114" t="s">
+        <v>121</v>
+      </c>
+      <c r="C114">
+        <v>166</v>
+      </c>
+      <c r="D114" t="s">
+        <v>6</v>
+      </c>
+      <c r="E114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>107</v>
+      </c>
+      <c r="B115" t="s">
+        <v>122</v>
+      </c>
+      <c r="C115">
+        <v>55</v>
+      </c>
+      <c r="D115" t="s">
+        <v>6</v>
+      </c>
+      <c r="E115" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>107</v>
+      </c>
+      <c r="B116" t="s">
+        <v>123</v>
+      </c>
+      <c r="C116">
+        <v>130</v>
+      </c>
+      <c r="D116" t="s">
+        <v>6</v>
+      </c>
+      <c r="E116" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>107</v>
+      </c>
+      <c r="B117" t="s">
+        <v>124</v>
+      </c>
+      <c r="C117">
+        <v>168</v>
+      </c>
+      <c r="D117" t="s">
+        <v>6</v>
+      </c>
+      <c r="E117" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>107</v>
+      </c>
+      <c r="B118" t="s">
+        <v>125</v>
+      </c>
+      <c r="C118">
+        <v>25</v>
+      </c>
+      <c r="D118" t="s">
+        <v>6</v>
+      </c>
+      <c r="E118" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>107</v>
+      </c>
+      <c r="B119" t="s">
+        <v>126</v>
+      </c>
+      <c r="C119">
+        <v>188</v>
+      </c>
+      <c r="D119" t="s">
+        <v>6</v>
+      </c>
+      <c r="E119" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>107</v>
+      </c>
+      <c r="B120" t="s">
+        <v>127</v>
+      </c>
+      <c r="C120">
+        <v>249</v>
+      </c>
+      <c r="D120" t="s">
+        <v>6</v>
+      </c>
+      <c r="E120" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>107</v>
+      </c>
+      <c r="B121" t="s">
+        <v>128</v>
+      </c>
+      <c r="C121">
+        <v>297</v>
+      </c>
+      <c r="D121" t="s">
+        <v>6</v>
+      </c>
+      <c r="E121" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>107</v>
+      </c>
+      <c r="B122" t="s">
+        <v>129</v>
+      </c>
+      <c r="C122">
+        <v>74</v>
+      </c>
+      <c r="D122" t="s">
+        <v>6</v>
+      </c>
+      <c r="E122" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>107</v>
+      </c>
+      <c r="B123" t="s">
+        <v>130</v>
+      </c>
+      <c r="C123">
+        <v>96</v>
+      </c>
+      <c r="D123" t="s">
+        <v>6</v>
+      </c>
+      <c r="E123" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>107</v>
+      </c>
+      <c r="B124" t="s">
+        <v>131</v>
+      </c>
+      <c r="C124">
+        <v>191</v>
+      </c>
+      <c r="D124" t="s">
+        <v>6</v>
+      </c>
+      <c r="E124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>107</v>
+      </c>
+      <c r="B125" t="s">
+        <v>132</v>
+      </c>
+      <c r="C125">
+        <v>104</v>
+      </c>
+      <c r="D125" t="s">
+        <v>6</v>
+      </c>
+      <c r="E125" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>107</v>
+      </c>
+      <c r="B126" t="s">
+        <v>133</v>
+      </c>
+      <c r="C126">
+        <v>48</v>
+      </c>
+      <c r="D126" t="s">
+        <v>6</v>
+      </c>
+      <c r="E126" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>107</v>
+      </c>
+      <c r="B127" t="s">
+        <v>134</v>
+      </c>
+      <c r="C127">
+        <v>254</v>
+      </c>
+      <c r="D127" t="s">
+        <v>6</v>
+      </c>
+      <c r="E127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>107</v>
+      </c>
+      <c r="B128" t="s">
+        <v>135</v>
+      </c>
+      <c r="C128">
+        <v>201</v>
+      </c>
+      <c r="D128" t="s">
+        <v>6</v>
+      </c>
+      <c r="E128" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>107</v>
+      </c>
+      <c r="B129" t="s">
+        <v>136</v>
+      </c>
+      <c r="C129">
+        <v>108</v>
+      </c>
+      <c r="D129" t="s">
+        <v>6</v>
+      </c>
+      <c r="E129" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>107</v>
+      </c>
+      <c r="B130" t="s">
+        <v>137</v>
+      </c>
+      <c r="C130">
+        <v>222</v>
+      </c>
+      <c r="D130" t="s">
+        <v>6</v>
+      </c>
+      <c r="E130" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>107</v>
+      </c>
+      <c r="B131" t="s">
+        <v>138</v>
+      </c>
+      <c r="C131">
+        <v>173</v>
+      </c>
+      <c r="D131" t="s">
+        <v>6</v>
+      </c>
+      <c r="E131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>107</v>
+      </c>
+      <c r="B132" t="s">
+        <v>139</v>
+      </c>
+      <c r="C132">
+        <v>186</v>
+      </c>
+      <c r="D132" t="s">
+        <v>6</v>
+      </c>
+      <c r="E132" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>107</v>
+      </c>
+      <c r="B133" t="s">
+        <v>140</v>
+      </c>
+      <c r="C133">
+        <v>87</v>
+      </c>
+      <c r="D133" t="s">
+        <v>6</v>
+      </c>
+      <c r="E133" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>107</v>
+      </c>
+      <c r="B134" t="s">
+        <v>141</v>
+      </c>
+      <c r="C134">
+        <v>111</v>
+      </c>
+      <c r="D134" t="s">
+        <v>6</v>
+      </c>
+      <c r="E134" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>107</v>
+      </c>
+      <c r="B135" t="s">
+        <v>142</v>
+      </c>
+      <c r="C135">
+        <v>182</v>
+      </c>
+      <c r="D135" t="s">
+        <v>6</v>
+      </c>
+      <c r="E135" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>107</v>
+      </c>
+      <c r="B136" t="s">
+        <v>143</v>
+      </c>
+      <c r="C136">
+        <v>90</v>
+      </c>
+      <c r="D136" t="s">
+        <v>6</v>
+      </c>
+      <c r="E136" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>107</v>
+      </c>
+      <c r="B137" t="s">
+        <v>144</v>
+      </c>
+      <c r="C137">
+        <v>12</v>
+      </c>
+      <c r="D137" t="s">
+        <v>6</v>
+      </c>
+      <c r="E137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>107</v>
+      </c>
+      <c r="B138" t="s">
+        <v>145</v>
+      </c>
+      <c r="C138">
+        <v>177</v>
+      </c>
+      <c r="D138" t="s">
+        <v>6</v>
+      </c>
+      <c r="E138" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>107</v>
+      </c>
+      <c r="B139" t="s">
+        <v>146</v>
+      </c>
+      <c r="C139">
+        <v>111</v>
+      </c>
+      <c r="D139" t="s">
+        <v>6</v>
+      </c>
+      <c r="E139" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>107</v>
+      </c>
+      <c r="B140" t="s">
+        <v>147</v>
+      </c>
+      <c r="C140">
+        <v>238</v>
+      </c>
+      <c r="D140" t="s">
+        <v>6</v>
+      </c>
+      <c r="E140" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>107</v>
+      </c>
+      <c r="B141" t="s">
+        <v>148</v>
+      </c>
+      <c r="C141">
+        <v>40</v>
+      </c>
+      <c r="D141" t="s">
+        <v>6</v>
+      </c>
+      <c r="E141" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>107</v>
+      </c>
+      <c r="B142" t="s">
+        <v>149</v>
+      </c>
+      <c r="C142">
+        <v>22</v>
+      </c>
+      <c r="D142" t="s">
+        <v>6</v>
+      </c>
+      <c r="E142" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>107</v>
+      </c>
+      <c r="B143" t="s">
+        <v>150</v>
+      </c>
+      <c r="C143">
+        <v>296</v>
+      </c>
+      <c r="D143" t="s">
+        <v>6</v>
+      </c>
+      <c r="E143" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>107</v>
+      </c>
+      <c r="B144" t="s">
+        <v>151</v>
+      </c>
+      <c r="C144">
+        <v>227</v>
+      </c>
+      <c r="D144" t="s">
+        <v>6</v>
+      </c>
+      <c r="E144" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>107</v>
+      </c>
+      <c r="B145" t="s">
+        <v>152</v>
+      </c>
+      <c r="C145">
+        <v>72</v>
+      </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+      <c r="E145" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>107</v>
+      </c>
+      <c r="B146" t="s">
+        <v>153</v>
+      </c>
+      <c r="C146">
+        <v>62</v>
+      </c>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+      <c r="E146" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>107</v>
+      </c>
+      <c r="B147" t="s">
+        <v>154</v>
+      </c>
+      <c r="C147">
+        <v>77</v>
+      </c>
+      <c r="D147" t="s">
+        <v>6</v>
+      </c>
+      <c r="E147" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>107</v>
+      </c>
+      <c r="B148" t="s">
+        <v>155</v>
+      </c>
+      <c r="C148">
+        <v>299</v>
+      </c>
+      <c r="D148" t="s">
+        <v>6</v>
+      </c>
+      <c r="E148" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>107</v>
+      </c>
+      <c r="B149" t="s">
+        <v>156</v>
+      </c>
+      <c r="C149">
+        <v>237</v>
+      </c>
+      <c r="D149" t="s">
+        <v>6</v>
+      </c>
+      <c r="E149" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>107</v>
+      </c>
+      <c r="B150" t="s">
+        <v>157</v>
+      </c>
+      <c r="C150">
+        <v>8</v>
+      </c>
+      <c r="D150" t="s">
+        <v>6</v>
+      </c>
+      <c r="E150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>107</v>
+      </c>
+      <c r="B151" t="s">
+        <v>158</v>
+      </c>
+      <c r="C151">
+        <v>212</v>
+      </c>
+      <c r="D151" t="s">
+        <v>6</v>
+      </c>
+      <c r="E151" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>107</v>
+      </c>
+      <c r="B152" t="s">
+        <v>159</v>
+      </c>
+      <c r="C152">
+        <v>189</v>
+      </c>
+      <c r="D152" t="s">
+        <v>6</v>
+      </c>
+      <c r="E152" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>107</v>
+      </c>
+      <c r="B153" t="s">
+        <v>160</v>
+      </c>
+      <c r="C153">
+        <v>216</v>
+      </c>
+      <c r="D153" t="s">
+        <v>6</v>
+      </c>
+      <c r="E153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>107</v>
+      </c>
+      <c r="B154" t="s">
+        <v>161</v>
+      </c>
+      <c r="C154">
+        <v>57</v>
+      </c>
+      <c r="D154" t="s">
+        <v>6</v>
+      </c>
+      <c r="E154" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>107</v>
+      </c>
+      <c r="B155" t="s">
+        <v>162</v>
+      </c>
+      <c r="C155">
+        <v>187</v>
+      </c>
+      <c r="D155" t="s">
+        <v>6</v>
+      </c>
+      <c r="E155" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>107</v>
+      </c>
+      <c r="B156" t="s">
+        <v>163</v>
+      </c>
+      <c r="C156">
+        <v>22</v>
+      </c>
+      <c r="D156" t="s">
+        <v>6</v>
+      </c>
+      <c r="E156" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>107</v>
+      </c>
+      <c r="B157" t="s">
+        <v>164</v>
+      </c>
+      <c r="C157">
+        <v>166</v>
+      </c>
+      <c r="D157" t="s">
+        <v>6</v>
+      </c>
+      <c r="E157" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>107</v>
+      </c>
+      <c r="B158" t="s">
+        <v>165</v>
+      </c>
+      <c r="C158">
+        <v>14</v>
+      </c>
+      <c r="D158" t="s">
+        <v>6</v>
+      </c>
+      <c r="E158" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>107</v>
+      </c>
+      <c r="B159" t="s">
+        <v>166</v>
+      </c>
+      <c r="C159">
+        <v>240</v>
+      </c>
+      <c r="D159" t="s">
+        <v>6</v>
+      </c>
+      <c r="E159" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>107</v>
+      </c>
+      <c r="B160" t="s">
+        <v>167</v>
+      </c>
+      <c r="C160">
+        <v>71</v>
+      </c>
+      <c r="D160" t="s">
+        <v>6</v>
+      </c>
+      <c r="E160" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>107</v>
+      </c>
+      <c r="B161" t="s">
+        <v>168</v>
+      </c>
+      <c r="C161">
+        <v>54</v>
+      </c>
+      <c r="D161" t="s">
+        <v>6</v>
+      </c>
+      <c r="E161" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>107</v>
+      </c>
+      <c r="B162" t="s">
+        <v>169</v>
+      </c>
+      <c r="C162">
+        <v>257</v>
+      </c>
+      <c r="D162" t="s">
+        <v>6</v>
+      </c>
+      <c r="E162" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>107</v>
+      </c>
+      <c r="B163" t="s">
+        <v>170</v>
+      </c>
+      <c r="C163">
+        <v>17</v>
+      </c>
+      <c r="D163" t="s">
+        <v>6</v>
+      </c>
+      <c r="E163" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>107</v>
+      </c>
+      <c r="B164" t="s">
+        <v>171</v>
+      </c>
+      <c r="C164">
+        <v>194</v>
+      </c>
+      <c r="D164" t="s">
+        <v>6</v>
+      </c>
+      <c r="E164" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>107</v>
+      </c>
+      <c r="B165" t="s">
+        <v>172</v>
+      </c>
+      <c r="C165">
+        <v>289</v>
+      </c>
+      <c r="D165" t="s">
+        <v>6</v>
+      </c>
+      <c r="E165" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>107</v>
+      </c>
+      <c r="B166" t="s">
+        <v>173</v>
+      </c>
+      <c r="C166">
+        <v>28</v>
+      </c>
+      <c r="D166" t="s">
+        <v>6</v>
+      </c>
+      <c r="E166" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>107</v>
+      </c>
+      <c r="B167" t="s">
+        <v>174</v>
+      </c>
+      <c r="C167">
+        <v>217</v>
+      </c>
+      <c r="D167" t="s">
+        <v>6</v>
+      </c>
+      <c r="E167" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>107</v>
+      </c>
+      <c r="B168" t="s">
+        <v>175</v>
+      </c>
+      <c r="C168">
+        <v>88</v>
+      </c>
+      <c r="D168" t="s">
+        <v>6</v>
+      </c>
+      <c r="E168" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>107</v>
+      </c>
+      <c r="B169" t="s">
+        <v>176</v>
+      </c>
+      <c r="C169">
+        <v>205</v>
+      </c>
+      <c r="D169" t="s">
+        <v>6</v>
+      </c>
+      <c r="E169" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>107</v>
+      </c>
+      <c r="B170" t="s">
+        <v>177</v>
+      </c>
+      <c r="C170">
+        <v>64</v>
+      </c>
+      <c r="D170" t="s">
+        <v>6</v>
+      </c>
+      <c r="E170" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>107</v>
+      </c>
+      <c r="B171" t="s">
+        <v>178</v>
+      </c>
+      <c r="C171">
+        <v>169</v>
+      </c>
+      <c r="D171" t="s">
+        <v>6</v>
+      </c>
+      <c r="E171" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>107</v>
+      </c>
+      <c r="B172" t="s">
+        <v>179</v>
+      </c>
+      <c r="C172">
+        <v>273</v>
+      </c>
+      <c r="D172" t="s">
+        <v>6</v>
+      </c>
+      <c r="E172" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>107</v>
+      </c>
+      <c r="B173" t="s">
+        <v>180</v>
+      </c>
+      <c r="C173">
+        <v>238</v>
+      </c>
+      <c r="D173" t="s">
+        <v>6</v>
+      </c>
+      <c r="E173" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>107</v>
+      </c>
+      <c r="B174" t="s">
+        <v>181</v>
+      </c>
+      <c r="C174">
+        <v>69</v>
+      </c>
+      <c r="D174" t="s">
+        <v>6</v>
+      </c>
+      <c r="E174" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>107</v>
+      </c>
+      <c r="B175" t="s">
+        <v>182</v>
+      </c>
+      <c r="C175">
+        <v>243</v>
+      </c>
+      <c r="D175" t="s">
+        <v>6</v>
+      </c>
+      <c r="E175" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>107</v>
+      </c>
+      <c r="B176" t="s">
+        <v>183</v>
+      </c>
+      <c r="C176">
+        <v>228</v>
+      </c>
+      <c r="D176" t="s">
+        <v>6</v>
+      </c>
+      <c r="E176" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>107</v>
+      </c>
+      <c r="B177" t="s">
+        <v>184</v>
+      </c>
+      <c r="C177">
+        <v>15</v>
+      </c>
+      <c r="D177" t="s">
+        <v>6</v>
+      </c>
+      <c r="E177" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>107</v>
+      </c>
+      <c r="B178" t="s">
+        <v>185</v>
+      </c>
+      <c r="C178">
+        <v>15</v>
+      </c>
+      <c r="D178" t="s">
+        <v>6</v>
+      </c>
+      <c r="E178" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>107</v>
+      </c>
+      <c r="B179" t="s">
+        <v>186</v>
+      </c>
+      <c r="C179">
+        <v>149</v>
+      </c>
+      <c r="D179" t="s">
+        <v>6</v>
+      </c>
+      <c r="E179" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>107</v>
+      </c>
+      <c r="B180" t="s">
+        <v>187</v>
+      </c>
+      <c r="C180">
+        <v>10</v>
+      </c>
+      <c r="D180" t="s">
+        <v>6</v>
+      </c>
+      <c r="E180" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>107</v>
+      </c>
+      <c r="B181" t="s">
+        <v>188</v>
+      </c>
+      <c r="C181">
+        <v>225</v>
+      </c>
+      <c r="D181" t="s">
+        <v>6</v>
+      </c>
+      <c r="E181" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>107</v>
+      </c>
+      <c r="B182" t="s">
+        <v>189</v>
+      </c>
+      <c r="C182">
+        <v>239</v>
+      </c>
+      <c r="D182" t="s">
+        <v>6</v>
+      </c>
+      <c r="E182" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>107</v>
+      </c>
+      <c r="B183" t="s">
+        <v>190</v>
+      </c>
+      <c r="C183">
+        <v>44</v>
+      </c>
+      <c r="D183" t="s">
+        <v>6</v>
+      </c>
+      <c r="E183" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>107</v>
+      </c>
+      <c r="B184" t="s">
+        <v>191</v>
+      </c>
+      <c r="C184">
+        <v>62</v>
+      </c>
+      <c r="D184" t="s">
+        <v>6</v>
+      </c>
+      <c r="E184" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>107</v>
+      </c>
+      <c r="B185" t="s">
+        <v>192</v>
+      </c>
+      <c r="C185">
+        <v>7</v>
+      </c>
+      <c r="D185" t="s">
+        <v>6</v>
+      </c>
+      <c r="E185" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>107</v>
+      </c>
+      <c r="B186" t="s">
+        <v>193</v>
+      </c>
+      <c r="C186">
+        <v>36</v>
+      </c>
+      <c r="D186" t="s">
+        <v>6</v>
+      </c>
+      <c r="E186" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>107</v>
+      </c>
+      <c r="B187" t="s">
+        <v>194</v>
+      </c>
+      <c r="C187">
+        <v>156</v>
+      </c>
+      <c r="D187" t="s">
+        <v>6</v>
+      </c>
+      <c r="E187" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>107</v>
+      </c>
+      <c r="B188" t="s">
+        <v>195</v>
+      </c>
+      <c r="C188">
+        <v>82</v>
+      </c>
+      <c r="D188" t="s">
+        <v>6</v>
+      </c>
+      <c r="E188" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>107</v>
+      </c>
+      <c r="B189" t="s">
+        <v>196</v>
+      </c>
+      <c r="C189">
+        <v>240</v>
+      </c>
+      <c r="D189" t="s">
+        <v>6</v>
+      </c>
+      <c r="E189" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>107</v>
+      </c>
+      <c r="B190" t="s">
+        <v>197</v>
+      </c>
+      <c r="C190">
+        <v>174</v>
+      </c>
+      <c r="D190" t="s">
+        <v>6</v>
+      </c>
+      <c r="E190" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>107</v>
+      </c>
+      <c r="B191" t="s">
+        <v>198</v>
+      </c>
+      <c r="C191">
+        <v>297</v>
+      </c>
+      <c r="D191" t="s">
+        <v>6</v>
+      </c>
+      <c r="E191" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>107</v>
+      </c>
+      <c r="B192" t="s">
+        <v>199</v>
+      </c>
+      <c r="C192">
+        <v>24</v>
+      </c>
+      <c r="D192" t="s">
+        <v>6</v>
+      </c>
+      <c r="E192" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>107</v>
+      </c>
+      <c r="B193" t="s">
+        <v>200</v>
+      </c>
+      <c r="C193">
+        <v>135</v>
+      </c>
+      <c r="D193" t="s">
+        <v>6</v>
+      </c>
+      <c r="E193" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>107</v>
+      </c>
+      <c r="B194" t="s">
+        <v>201</v>
+      </c>
+      <c r="C194">
+        <v>34</v>
+      </c>
+      <c r="D194" t="s">
+        <v>6</v>
+      </c>
+      <c r="E194" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>107</v>
+      </c>
+      <c r="B195" t="s">
+        <v>202</v>
+      </c>
+      <c r="C195">
+        <v>42</v>
+      </c>
+      <c r="D195" t="s">
+        <v>6</v>
+      </c>
+      <c r="E195" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>107</v>
+      </c>
+      <c r="B196" t="s">
+        <v>203</v>
+      </c>
+      <c r="C196">
+        <v>280</v>
+      </c>
+      <c r="D196" t="s">
+        <v>6</v>
+      </c>
+      <c r="E196" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>107</v>
+      </c>
+      <c r="B197" t="s">
+        <v>204</v>
+      </c>
+      <c r="C197">
+        <v>136</v>
+      </c>
+      <c r="D197" t="s">
+        <v>6</v>
+      </c>
+      <c r="E197" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>107</v>
+      </c>
+      <c r="B198" t="s">
+        <v>205</v>
+      </c>
+      <c r="C198">
+        <v>172</v>
+      </c>
+      <c r="D198" t="s">
+        <v>6</v>
+      </c>
+      <c r="E198" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>107</v>
+      </c>
+      <c r="B199" t="s">
+        <v>206</v>
+      </c>
+      <c r="C199">
+        <v>239</v>
+      </c>
+      <c r="D199" t="s">
+        <v>6</v>
+      </c>
+      <c r="E199" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>207</v>
+      </c>
+      <c r="B200" t="s">
+        <v>208</v>
+      </c>
+      <c r="C200">
+        <v>7.57</v>
+      </c>
+      <c r="D200" t="s">
+        <v>209</v>
+      </c>
+      <c r="E200" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>207</v>
+      </c>
+      <c r="B201" t="s">
+        <v>211</v>
+      </c>
+      <c r="C201">
+        <v>14.76</v>
+      </c>
+      <c r="D201" t="s">
+        <v>209</v>
+      </c>
+      <c r="E201" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>207</v>
+      </c>
+      <c r="B202" t="s">
+        <v>212</v>
+      </c>
+      <c r="C202">
+        <v>16.05</v>
+      </c>
+      <c r="D202" t="s">
+        <v>209</v>
+      </c>
+      <c r="E202" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>207</v>
+      </c>
+      <c r="B203" t="s">
+        <v>213</v>
+      </c>
+      <c r="C203">
+        <v>4.84</v>
+      </c>
+      <c r="D203" t="s">
+        <v>209</v>
+      </c>
+      <c r="E203" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>207</v>
+      </c>
+      <c r="B204" t="s">
+        <v>214</v>
+      </c>
+      <c r="C204">
+        <v>13.45</v>
+      </c>
+      <c r="D204" t="s">
+        <v>209</v>
+      </c>
+      <c r="E204" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>207</v>
+      </c>
+      <c r="B205" t="s">
+        <v>215</v>
+      </c>
+      <c r="C205">
+        <v>3.78</v>
+      </c>
+      <c r="D205" t="s">
+        <v>209</v>
+      </c>
+      <c r="E205" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>207</v>
+      </c>
+      <c r="B206" t="s">
+        <v>216</v>
+      </c>
+      <c r="C206">
+        <v>22.5</v>
+      </c>
+      <c r="D206" t="s">
+        <v>209</v>
+      </c>
+      <c r="E206" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>207</v>
+      </c>
+      <c r="B207" t="s">
+        <v>217</v>
+      </c>
+      <c r="C207">
+        <v>20.27</v>
+      </c>
+      <c r="D207" t="s">
+        <v>209</v>
+      </c>
+      <c r="E207" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>207</v>
+      </c>
+      <c r="B208" t="s">
+        <v>218</v>
+      </c>
+      <c r="C208">
+        <v>16.28</v>
+      </c>
+      <c r="D208" t="s">
+        <v>209</v>
+      </c>
+      <c r="E208" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>207</v>
+      </c>
+      <c r="B209" t="s">
+        <v>219</v>
+      </c>
+      <c r="C209">
+        <v>3.36</v>
+      </c>
+      <c r="D209" t="s">
+        <v>209</v>
+      </c>
+      <c r="E209" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>207</v>
+      </c>
+      <c r="B210" t="s">
+        <v>220</v>
+      </c>
+      <c r="C210">
+        <v>4</v>
+      </c>
+      <c r="D210" t="s">
+        <v>209</v>
+      </c>
+      <c r="E210" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>207</v>
+      </c>
+      <c r="B211" t="s">
+        <v>221</v>
+      </c>
+      <c r="C211">
+        <v>17.21</v>
+      </c>
+      <c r="D211" t="s">
+        <v>209</v>
+      </c>
+      <c r="E211" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>207</v>
+      </c>
+      <c r="B212" t="s">
+        <v>222</v>
+      </c>
+      <c r="C212">
+        <v>20.07</v>
+      </c>
+      <c r="D212" t="s">
+        <v>209</v>
+      </c>
+      <c r="E212" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>207</v>
+      </c>
+      <c r="B213" t="s">
+        <v>223</v>
+      </c>
+      <c r="C213">
+        <v>14</v>
+      </c>
+      <c r="D213" t="s">
+        <v>209</v>
+      </c>
+      <c r="E213" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>207</v>
+      </c>
+      <c r="B214" t="s">
+        <v>224</v>
+      </c>
+      <c r="C214">
+        <v>17.41</v>
+      </c>
+      <c r="D214" t="s">
+        <v>209</v>
+      </c>
+      <c r="E214" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>207</v>
+      </c>
+      <c r="B215" t="s">
+        <v>225</v>
+      </c>
+      <c r="C215">
+        <v>12.5</v>
+      </c>
+      <c r="D215" t="s">
+        <v>209</v>
+      </c>
+      <c r="E215" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>207</v>
+      </c>
+      <c r="B216" t="s">
+        <v>226</v>
+      </c>
+      <c r="C216">
+        <v>14.14</v>
+      </c>
+      <c r="D216" t="s">
+        <v>209</v>
+      </c>
+      <c r="E216" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>207</v>
+      </c>
+      <c r="B217" t="s">
+        <v>227</v>
+      </c>
+      <c r="C217">
+        <v>19.03</v>
+      </c>
+      <c r="D217" t="s">
+        <v>209</v>
+      </c>
+      <c r="E217" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>207</v>
+      </c>
+      <c r="B218" t="s">
+        <v>228</v>
+      </c>
+      <c r="C218">
+        <v>23</v>
+      </c>
+      <c r="D218" t="s">
+        <v>209</v>
+      </c>
+      <c r="E218" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>207</v>
+      </c>
+      <c r="B219" t="s">
+        <v>229</v>
+      </c>
+      <c r="C219">
+        <v>9.6199999999999992</v>
+      </c>
+      <c r="D219" t="s">
+        <v>209</v>
+      </c>
+      <c r="E219" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>207</v>
+      </c>
+      <c r="B220" t="s">
+        <v>230</v>
+      </c>
+      <c r="C220">
+        <v>2.86</v>
+      </c>
+      <c r="D220" t="s">
+        <v>209</v>
+      </c>
+      <c r="E220" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>207</v>
+      </c>
+      <c r="B221" t="s">
+        <v>231</v>
+      </c>
+      <c r="C221">
+        <v>10.83</v>
+      </c>
+      <c r="D221" t="s">
+        <v>209</v>
+      </c>
+      <c r="E221" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>207</v>
+      </c>
+      <c r="B222" t="s">
+        <v>232</v>
+      </c>
+      <c r="C222">
+        <v>11.93</v>
+      </c>
+      <c r="D222" t="s">
+        <v>209</v>
+      </c>
+      <c r="E222" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>207</v>
+      </c>
+      <c r="B223" t="s">
+        <v>233</v>
+      </c>
+      <c r="C223">
+        <v>3.43</v>
+      </c>
+      <c r="D223" t="s">
+        <v>209</v>
+      </c>
+      <c r="E223" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>207</v>
+      </c>
+      <c r="B224" t="s">
+        <v>234</v>
+      </c>
+      <c r="C224">
+        <v>17.579999999999998</v>
+      </c>
+      <c r="D224" t="s">
+        <v>209</v>
+      </c>
+      <c r="E224" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>207</v>
+      </c>
+      <c r="B225" t="s">
+        <v>235</v>
+      </c>
+      <c r="C225">
+        <v>17.16</v>
+      </c>
+      <c r="D225" t="s">
+        <v>209</v>
+      </c>
+      <c r="E225" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>207</v>
+      </c>
+      <c r="B226" t="s">
+        <v>236</v>
+      </c>
+      <c r="C226">
+        <v>21.24</v>
+      </c>
+      <c r="D226" t="s">
+        <v>209</v>
+      </c>
+      <c r="E226" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>207</v>
+      </c>
+      <c r="B227" t="s">
+        <v>237</v>
+      </c>
+      <c r="C227">
+        <v>2.54</v>
+      </c>
+      <c r="D227" t="s">
+        <v>209</v>
+      </c>
+      <c r="E227" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>207</v>
+      </c>
+      <c r="B228" t="s">
+        <v>238</v>
+      </c>
+      <c r="C228">
+        <v>12.22</v>
+      </c>
+      <c r="D228" t="s">
+        <v>209</v>
+      </c>
+      <c r="E228" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>207</v>
+      </c>
+      <c r="B229" t="s">
+        <v>239</v>
+      </c>
+      <c r="C229">
+        <v>8.75</v>
+      </c>
+      <c r="D229" t="s">
+        <v>209</v>
+      </c>
+      <c r="E229" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>207</v>
+      </c>
+      <c r="B230" t="s">
+        <v>240</v>
+      </c>
+      <c r="C230">
+        <v>3.45</v>
+      </c>
+      <c r="D230" t="s">
+        <v>209</v>
+      </c>
+      <c r="E230" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>207</v>
+      </c>
+      <c r="B231" t="s">
+        <v>241</v>
+      </c>
+      <c r="C231">
+        <v>8.8699999999999992</v>
+      </c>
+      <c r="D231" t="s">
+        <v>209</v>
+      </c>
+      <c r="E231" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>207</v>
+      </c>
+      <c r="B232" t="s">
+        <v>242</v>
+      </c>
+      <c r="C232">
+        <v>5.26</v>
+      </c>
+      <c r="D232" t="s">
+        <v>209</v>
+      </c>
+      <c r="E232" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>207</v>
+      </c>
+      <c r="B233" t="s">
+        <v>243</v>
+      </c>
+      <c r="C233">
+        <v>5.33</v>
+      </c>
+      <c r="D233" t="s">
+        <v>209</v>
+      </c>
+      <c r="E233" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>207</v>
+      </c>
+      <c r="B234" t="s">
+        <v>244</v>
+      </c>
+      <c r="C234">
+        <v>9.1199999999999992</v>
+      </c>
+      <c r="D234" t="s">
+        <v>209</v>
+      </c>
+      <c r="E234" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>207</v>
+      </c>
+      <c r="B235" t="s">
+        <v>245</v>
+      </c>
+      <c r="C235">
+        <v>18.11</v>
+      </c>
+      <c r="D235" t="s">
+        <v>209</v>
+      </c>
+      <c r="E235" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>207</v>
+      </c>
+      <c r="B236" t="s">
+        <v>246</v>
+      </c>
+      <c r="C236">
+        <v>16.350000000000001</v>
+      </c>
+      <c r="D236" t="s">
+        <v>209</v>
+      </c>
+      <c r="E236" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>207</v>
+      </c>
+      <c r="B237" t="s">
+        <v>247</v>
+      </c>
+      <c r="C237">
+        <v>19.850000000000001</v>
+      </c>
+      <c r="D237" t="s">
+        <v>209</v>
+      </c>
+      <c r="E237" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>207</v>
+      </c>
+      <c r="B238" t="s">
+        <v>248</v>
+      </c>
+      <c r="C238">
+        <v>17.71</v>
+      </c>
+      <c r="D238" t="s">
+        <v>209</v>
+      </c>
+      <c r="E238" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>207</v>
+      </c>
+      <c r="B239" t="s">
+        <v>249</v>
+      </c>
+      <c r="C239">
+        <v>4.2699999999999996</v>
+      </c>
+      <c r="D239" t="s">
+        <v>209</v>
+      </c>
+      <c r="E239" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>207</v>
+      </c>
+      <c r="B240" t="s">
+        <v>250</v>
+      </c>
+      <c r="C240">
+        <v>12.45</v>
+      </c>
+      <c r="D240" t="s">
+        <v>209</v>
+      </c>
+      <c r="E240" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>207</v>
+      </c>
+      <c r="B241" t="s">
+        <v>251</v>
+      </c>
+      <c r="C241">
+        <v>9.11</v>
+      </c>
+      <c r="D241" t="s">
+        <v>209</v>
+      </c>
+      <c r="E241" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>207</v>
+      </c>
+      <c r="B242" t="s">
+        <v>252</v>
+      </c>
+      <c r="C242">
+        <v>18.18</v>
+      </c>
+      <c r="D242" t="s">
+        <v>209</v>
+      </c>
+      <c r="E242" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>207</v>
+      </c>
+      <c r="B243" t="s">
+        <v>253</v>
+      </c>
+      <c r="C243">
+        <v>7.94</v>
+      </c>
+      <c r="D243" t="s">
+        <v>209</v>
+      </c>
+      <c r="E243" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>207</v>
+      </c>
+      <c r="B244" t="s">
+        <v>254</v>
+      </c>
+      <c r="C244">
+        <v>14.99</v>
+      </c>
+      <c r="D244" t="s">
+        <v>209</v>
+      </c>
+      <c r="E244" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>207</v>
+      </c>
+      <c r="B245" t="s">
+        <v>255</v>
+      </c>
+      <c r="C245">
+        <v>21.52</v>
+      </c>
+      <c r="D245" t="s">
+        <v>209</v>
+      </c>
+      <c r="E245" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>207</v>
+      </c>
+      <c r="B246" t="s">
+        <v>256</v>
+      </c>
+      <c r="C246">
+        <v>14.56</v>
+      </c>
+      <c r="D246" t="s">
+        <v>209</v>
+      </c>
+      <c r="E246" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>207</v>
+      </c>
+      <c r="B247" t="s">
+        <v>257</v>
+      </c>
+      <c r="C247">
+        <v>6.81</v>
+      </c>
+      <c r="D247" t="s">
+        <v>209</v>
+      </c>
+      <c r="E247" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>207</v>
+      </c>
+      <c r="B248" t="s">
+        <v>258</v>
+      </c>
+      <c r="C248">
+        <v>11.99</v>
+      </c>
+      <c r="D248" t="s">
+        <v>209</v>
+      </c>
+      <c r="E248" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>207</v>
+      </c>
+      <c r="B249" t="s">
+        <v>259</v>
+      </c>
+      <c r="C249">
+        <v>18.97</v>
+      </c>
+      <c r="D249" t="s">
+        <v>209</v>
+      </c>
+      <c r="E249" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>207</v>
+      </c>
+      <c r="B250" t="s">
+        <v>260</v>
+      </c>
+      <c r="C250">
+        <v>10.58</v>
+      </c>
+      <c r="D250" t="s">
+        <v>209</v>
+      </c>
+      <c r="E250" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>207</v>
+      </c>
+      <c r="B251" t="s">
+        <v>261</v>
+      </c>
+      <c r="C251">
+        <v>12.55</v>
+      </c>
+      <c r="D251" t="s">
+        <v>209</v>
+      </c>
+      <c r="E251" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>207</v>
+      </c>
+      <c r="B252" t="s">
+        <v>262</v>
+      </c>
+      <c r="C252">
+        <v>18.59</v>
+      </c>
+      <c r="D252" t="s">
+        <v>209</v>
+      </c>
+      <c r="E252" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>207</v>
+      </c>
+      <c r="B253" t="s">
+        <v>263</v>
+      </c>
+      <c r="C253">
+        <v>13.17</v>
+      </c>
+      <c r="D253" t="s">
+        <v>209</v>
+      </c>
+      <c r="E253" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>207</v>
+      </c>
+      <c r="B254" t="s">
+        <v>264</v>
+      </c>
+      <c r="C254">
+        <v>11.74</v>
+      </c>
+      <c r="D254" t="s">
+        <v>209</v>
+      </c>
+      <c r="E254" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>207</v>
+      </c>
+      <c r="B255" t="s">
+        <v>265</v>
+      </c>
+      <c r="C255">
+        <v>12.39</v>
+      </c>
+      <c r="D255" t="s">
+        <v>209</v>
+      </c>
+      <c r="E255" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>207</v>
+      </c>
+      <c r="B256" t="s">
+        <v>266</v>
+      </c>
+      <c r="C256">
+        <v>16.920000000000002</v>
+      </c>
+      <c r="D256" t="s">
+        <v>209</v>
+      </c>
+      <c r="E256" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>207</v>
+      </c>
+      <c r="B257" t="s">
+        <v>267</v>
+      </c>
+      <c r="C257">
+        <v>17.97</v>
+      </c>
+      <c r="D257" t="s">
+        <v>209</v>
+      </c>
+      <c r="E257" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>207</v>
+      </c>
+      <c r="B258" t="s">
+        <v>268</v>
+      </c>
+      <c r="C258">
+        <v>14.5</v>
+      </c>
+      <c r="D258" t="s">
+        <v>209</v>
+      </c>
+      <c r="E258" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>207</v>
+      </c>
+      <c r="B259" t="s">
+        <v>269</v>
+      </c>
+      <c r="C259">
+        <v>19.96</v>
+      </c>
+      <c r="D259" t="s">
+        <v>209</v>
+      </c>
+      <c r="E259" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>207</v>
+      </c>
+      <c r="B260" t="s">
+        <v>270</v>
+      </c>
+      <c r="C260">
+        <v>16.79</v>
+      </c>
+      <c r="D260" t="s">
+        <v>209</v>
+      </c>
+      <c r="E260" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>207</v>
+      </c>
+      <c r="B261" t="s">
+        <v>271</v>
+      </c>
+      <c r="C261">
+        <v>17.13</v>
+      </c>
+      <c r="D261" t="s">
+        <v>209</v>
+      </c>
+      <c r="E261" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>207</v>
+      </c>
+      <c r="B262" t="s">
+        <v>272</v>
+      </c>
+      <c r="C262">
+        <v>7.26</v>
+      </c>
+      <c r="D262" t="s">
+        <v>209</v>
+      </c>
+      <c r="E262" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>207</v>
+      </c>
+      <c r="B263" t="s">
+        <v>273</v>
+      </c>
+      <c r="C263">
+        <v>7.89</v>
+      </c>
+      <c r="D263" t="s">
+        <v>209</v>
+      </c>
+      <c r="E263" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>207</v>
+      </c>
+      <c r="B264" t="s">
+        <v>274</v>
+      </c>
+      <c r="C264">
+        <v>11.86</v>
+      </c>
+      <c r="D264" t="s">
+        <v>209</v>
+      </c>
+      <c r="E264" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>207</v>
+      </c>
+      <c r="B265" t="s">
+        <v>275</v>
+      </c>
+      <c r="C265">
+        <v>10.66</v>
+      </c>
+      <c r="D265" t="s">
+        <v>209</v>
+      </c>
+      <c r="E265" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>207</v>
+      </c>
+      <c r="B266" t="s">
+        <v>276</v>
+      </c>
+      <c r="C266">
+        <v>9.89</v>
+      </c>
+      <c r="D266" t="s">
+        <v>209</v>
+      </c>
+      <c r="E266" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>207</v>
+      </c>
+      <c r="B267" t="s">
+        <v>277</v>
+      </c>
+      <c r="C267">
+        <v>16.420000000000002</v>
+      </c>
+      <c r="D267" t="s">
+        <v>209</v>
+      </c>
+      <c r="E267" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>207</v>
+      </c>
+      <c r="B268" t="s">
+        <v>278</v>
+      </c>
+      <c r="C268">
+        <v>11.05</v>
+      </c>
+      <c r="D268" t="s">
+        <v>209</v>
+      </c>
+      <c r="E268" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>207</v>
+      </c>
+      <c r="B269" t="s">
+        <v>279</v>
+      </c>
+      <c r="C269">
+        <v>24.74</v>
+      </c>
+      <c r="D269" t="s">
+        <v>209</v>
+      </c>
+      <c r="E269" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>207</v>
+      </c>
+      <c r="B270" t="s">
+        <v>280</v>
+      </c>
+      <c r="C270">
+        <v>14.34</v>
+      </c>
+      <c r="D270" t="s">
+        <v>209</v>
+      </c>
+      <c r="E270" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>207</v>
+      </c>
+      <c r="B271" t="s">
+        <v>281</v>
+      </c>
+      <c r="C271">
+        <v>19.86</v>
+      </c>
+      <c r="D271" t="s">
+        <v>209</v>
+      </c>
+      <c r="E271" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>207</v>
+      </c>
+      <c r="B272" t="s">
+        <v>282</v>
+      </c>
+      <c r="C272">
+        <v>15.92</v>
+      </c>
+      <c r="D272" t="s">
+        <v>209</v>
+      </c>
+      <c r="E272" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>207</v>
+      </c>
+      <c r="B273" t="s">
+        <v>283</v>
+      </c>
+      <c r="C273">
+        <v>19.14</v>
+      </c>
+      <c r="D273" t="s">
+        <v>209</v>
+      </c>
+      <c r="E273" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>207</v>
+      </c>
+      <c r="B274" t="s">
+        <v>284</v>
+      </c>
+      <c r="C274">
+        <v>17.91</v>
+      </c>
+      <c r="D274" t="s">
+        <v>209</v>
+      </c>
+      <c r="E274" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>207</v>
+      </c>
+      <c r="B275" t="s">
+        <v>285</v>
+      </c>
+      <c r="C275">
+        <v>17.79</v>
+      </c>
+      <c r="D275" t="s">
+        <v>209</v>
+      </c>
+      <c r="E275" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>207</v>
+      </c>
+      <c r="B276" t="s">
+        <v>286</v>
+      </c>
+      <c r="C276">
+        <v>10.32</v>
+      </c>
+      <c r="D276" t="s">
+        <v>209</v>
+      </c>
+      <c r="E276" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>207</v>
+      </c>
+      <c r="B277" t="s">
+        <v>287</v>
+      </c>
+      <c r="C277">
+        <v>4.9400000000000004</v>
+      </c>
+      <c r="D277" t="s">
+        <v>209</v>
+      </c>
+      <c r="E277" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>207</v>
+      </c>
+      <c r="B278" t="s">
+        <v>288</v>
+      </c>
+      <c r="C278">
+        <v>8.08</v>
+      </c>
+      <c r="D278" t="s">
+        <v>209</v>
+      </c>
+      <c r="E278" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>207</v>
+      </c>
+      <c r="B279" t="s">
+        <v>289</v>
+      </c>
+      <c r="C279">
+        <v>13.75</v>
+      </c>
+      <c r="D279" t="s">
+        <v>209</v>
+      </c>
+      <c r="E279" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>207</v>
+      </c>
+      <c r="B280" t="s">
+        <v>290</v>
+      </c>
+      <c r="C280">
+        <v>7</v>
+      </c>
+      <c r="D280" t="s">
+        <v>209</v>
+      </c>
+      <c r="E280" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>207</v>
+      </c>
+      <c r="B281" t="s">
+        <v>291</v>
+      </c>
+      <c r="C281">
+        <v>19.25</v>
+      </c>
+      <c r="D281" t="s">
+        <v>209</v>
+      </c>
+      <c r="E281" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>207</v>
+      </c>
+      <c r="B282" t="s">
+        <v>292</v>
+      </c>
+      <c r="C282">
+        <v>13.23</v>
+      </c>
+      <c r="D282" t="s">
+        <v>209</v>
+      </c>
+      <c r="E282" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>207</v>
+      </c>
+      <c r="B283" t="s">
+        <v>293</v>
+      </c>
+      <c r="C283">
+        <v>16.190000000000001</v>
+      </c>
+      <c r="D283" t="s">
+        <v>209</v>
+      </c>
+      <c r="E283" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>207</v>
+      </c>
+      <c r="B284" t="s">
+        <v>294</v>
+      </c>
+      <c r="C284">
+        <v>3.99</v>
+      </c>
+      <c r="D284" t="s">
+        <v>209</v>
+      </c>
+      <c r="E284" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>207</v>
+      </c>
+      <c r="B285" t="s">
+        <v>295</v>
+      </c>
+      <c r="C285">
+        <v>17.29</v>
+      </c>
+      <c r="D285" t="s">
+        <v>209</v>
+      </c>
+      <c r="E285" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>207</v>
+      </c>
+      <c r="B286" t="s">
+        <v>296</v>
+      </c>
+      <c r="C286">
+        <v>13.84</v>
+      </c>
+      <c r="D286" t="s">
+        <v>209</v>
+      </c>
+      <c r="E286" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A287" t="s">
+        <v>207</v>
+      </c>
+      <c r="B287" t="s">
+        <v>297</v>
+      </c>
+      <c r="C287">
+        <v>24.51</v>
+      </c>
+      <c r="D287" t="s">
+        <v>209</v>
+      </c>
+      <c r="E287" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A288" t="s">
+        <v>207</v>
+      </c>
+      <c r="B288" t="s">
+        <v>298</v>
+      </c>
+      <c r="C288">
+        <v>3.36</v>
+      </c>
+      <c r="D288" t="s">
+        <v>209</v>
+      </c>
+      <c r="E288" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A289" t="s">
+        <v>207</v>
+      </c>
+      <c r="B289" t="s">
+        <v>299</v>
+      </c>
+      <c r="C289">
+        <v>20.260000000000002</v>
+      </c>
+      <c r="D289" t="s">
+        <v>209</v>
+      </c>
+      <c r="E289" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A290" t="s">
+        <v>207</v>
+      </c>
+      <c r="B290" t="s">
+        <v>300</v>
+      </c>
+      <c r="C290">
+        <v>3.98</v>
+      </c>
+      <c r="D290" t="s">
+        <v>209</v>
+      </c>
+      <c r="E290" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A291" t="s">
+        <v>207</v>
+      </c>
+      <c r="B291" t="s">
+        <v>301</v>
+      </c>
+      <c r="C291">
+        <v>13.54</v>
+      </c>
+      <c r="D291" t="s">
+        <v>209</v>
+      </c>
+      <c r="E291" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A292" t="s">
+        <v>207</v>
+      </c>
+      <c r="B292" t="s">
+        <v>302</v>
+      </c>
+      <c r="C292">
+        <v>4.22</v>
+      </c>
+      <c r="D292" t="s">
+        <v>209</v>
+      </c>
+      <c r="E292" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A293" t="s">
+        <v>207</v>
+      </c>
+      <c r="B293" t="s">
+        <v>303</v>
+      </c>
+      <c r="C293">
+        <v>15.22</v>
+      </c>
+      <c r="D293" t="s">
+        <v>209</v>
+      </c>
+      <c r="E293" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>207</v>
+      </c>
+      <c r="B294" t="s">
+        <v>304</v>
+      </c>
+      <c r="C294">
+        <v>20.84</v>
+      </c>
+      <c r="D294" t="s">
+        <v>209</v>
+      </c>
+      <c r="E294" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>207</v>
+      </c>
+      <c r="B295" t="s">
+        <v>305</v>
+      </c>
+      <c r="C295">
+        <v>21.27</v>
+      </c>
+      <c r="D295" t="s">
+        <v>209</v>
+      </c>
+      <c r="E295" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>207</v>
+      </c>
+      <c r="B296" t="s">
+        <v>306</v>
+      </c>
+      <c r="C296">
+        <v>11.78</v>
+      </c>
+      <c r="D296" t="s">
+        <v>209</v>
+      </c>
+      <c r="E296" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>207</v>
+      </c>
+      <c r="B297" t="s">
+        <v>307</v>
+      </c>
+      <c r="C297">
+        <v>21.12</v>
+      </c>
+      <c r="D297" t="s">
+        <v>209</v>
+      </c>
+      <c r="E297" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>207</v>
+      </c>
+      <c r="B298" t="s">
+        <v>308</v>
+      </c>
+      <c r="C298">
+        <v>14.33</v>
+      </c>
+      <c r="D298" t="s">
+        <v>209</v>
+      </c>
+      <c r="E298" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>309</v>
+      </c>
+      <c r="B299" t="s">
+        <v>310</v>
+      </c>
+      <c r="C299">
+        <v>283</v>
+      </c>
+      <c r="D299" t="s">
+        <v>6</v>
+      </c>
+      <c r="E299" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>309</v>
+      </c>
+      <c r="B300" t="s">
+        <v>311</v>
+      </c>
+      <c r="C300">
+        <v>197</v>
+      </c>
+      <c r="D300" t="s">
+        <v>6</v>
+      </c>
+      <c r="E300" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>309</v>
+      </c>
+      <c r="B301" t="s">
+        <v>312</v>
+      </c>
+      <c r="C301">
+        <v>54</v>
+      </c>
+      <c r="D301" t="s">
+        <v>6</v>
+      </c>
+      <c r="E301" t="s">
         <v>5</v>
       </c>
     </row>
